--- a/docs/数值分析_模块怪物波次.xlsx
+++ b/docs/数值分析_模块怪物波次.xlsx
@@ -471,7 +471,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B26"/>
+  <dimension ref="A1:B27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -563,7 +563,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>黄=向上取整(红×50%)；蓝=红×4；红HP仅在波6/11换档：10→25→50</t>
+          <t>黄=向上取整(红×50%)；蓝=红×4；红HP在波6/11/16/21换档：10→25→50→80→130</t>
         </is>
       </c>
     </row>
@@ -575,7 +575,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>stage = (wave-1)//5 → 波1-5=0，6-10=1，11-15=2</t>
+          <t>stage = (wave-1)//5 → 波1-5=0 … 波21-25=4；价含稀有度倍率</t>
         </is>
       </c>
     </row>
@@ -587,7 +587,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>波5、10结束后三选一</t>
+          <t>波5/10/15/20 结束后三选一</t>
         </is>
       </c>
     </row>
@@ -599,159 +599,171 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>波3/6/9/12 三选一</t>
+          <t>每3波（至24）；波≥9 可抽黑洞</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr"/>
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>祝福束缚</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>波5/10/15/20：祝福+束缚组合三选一</t>
+        </is>
+      </c>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="inlineStr">
-        <is>
-          <t>工作表</t>
-        </is>
-      </c>
+      <c r="A14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>01_全局常量</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>开局资源、棋盘、返还率等</t>
+          <t>工作表</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>02_怪物</t>
+          <t>01_全局常量</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>三类怪 HP关系、速度及关键波HP</t>
+          <t>开局资源、棋盘、返还率等</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>03_模块_激光</t>
+          <t>02_怪物</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Lv1-5 伤害/储能/射速/伤每能</t>
+          <t>三类怪 HP关系、速度及关键波HP</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>04_模块_炸弹</t>
+          <t>03_模块_激光</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Lv1-5 伤害/AOE/能耗</t>
+          <t>Lv1-5 伤害/储能/射速/伤每能</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>05_模块_寒冰</t>
+          <t>04_模块_炸弹</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Lv1-5 控制参数</t>
+          <t>Lv1-5 伤害/AOE/能耗</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>06_模块_采矿</t>
+          <t>05_模块_寒冰</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Lv1-3 能耗与金产出</t>
+          <t>Lv1-5 控制参数</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>07_收束器</t>
+          <t>06_模块_采矿</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>路径模块</t>
+          <t>Lv1-3 能耗与金产出</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>08_发射器</t>
+          <t>07_收束器</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>四维升级档位与能量/秒</t>
+          <t>路径模块</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>09_波次曲线</t>
+          <t>08_发射器</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>15波固定配额/HP/总HP/间隔/刷怪段/验收时长</t>
+          <t>四维升级档位与能量/秒</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>10_商店价格</t>
+          <t>09_波次曲线</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>各模块在波1/6/11 的标价</t>
+          <t>25波固定配额/HP/总HP/间隔/刷怪段/验收时长</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>11_能量DPS对照</t>
+          <t>10_商店价格</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>无环理论DPS vs 波次总HP粗估</t>
+          <t>各模块（含黑洞）在关键波标价</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
+          <t>11_能量DPS对照</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>无环理论DPS vs 波次总HP粗估</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="inlineStr">
+        <is>
           <t>12_拆除费</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr">
+      <c r="B27" t="inlineStr">
         <is>
           <t>战斗中移动/拆除费用示例</t>
         </is>
@@ -768,7 +780,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V16"/>
+  <dimension ref="A1:V26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -792,7 +804,7 @@
     <col width="10" customWidth="1" min="19" max="19"/>
     <col width="10" customWidth="1" min="20" max="20"/>
     <col width="10" customWidth="1" min="21" max="21"/>
-    <col width="10" customWidth="1" min="22" max="22"/>
+    <col width="18" customWidth="1" min="22" max="22"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1249,7 +1261,7 @@
       </c>
       <c r="V6" s="3" t="inlineStr">
         <is>
-          <t>发射器升级</t>
+          <t>发射器+祝福束缚</t>
         </is>
       </c>
     </row>
@@ -1601,7 +1613,7 @@
       </c>
       <c r="V11" s="3" t="inlineStr">
         <is>
-          <t>发射器升级</t>
+          <t>发射器+祝福束缚</t>
         </is>
       </c>
     </row>
@@ -1947,7 +1959,707 @@
       <c r="U16" s="3" t="n">
         <v>23</v>
       </c>
-      <c r="V16" s="3" t="inlineStr"/>
+      <c r="V16" s="3" t="inlineStr">
+        <is>
+          <t>模块Draft+发射器+祝福束缚</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="C17" s="3" t="n">
+        <v>40</v>
+      </c>
+      <c r="D17" s="3" t="n">
+        <v>68</v>
+      </c>
+      <c r="E17" s="3" t="n">
+        <v>11</v>
+      </c>
+      <c r="F17" s="3" t="n">
+        <v>119</v>
+      </c>
+      <c r="G17" s="3" t="n">
+        <v>80</v>
+      </c>
+      <c r="H17" s="3" t="n">
+        <v>40</v>
+      </c>
+      <c r="I17" s="3" t="n">
+        <v>320</v>
+      </c>
+      <c r="J17" s="3" t="n">
+        <v>9440</v>
+      </c>
+      <c r="K17" s="5" t="n">
+        <v>0.7811320754716982</v>
+      </c>
+      <c r="L17" s="3" t="n">
+        <v>488</v>
+      </c>
+      <c r="M17" s="3" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="N17" s="3" t="n">
+        <v>28.1</v>
+      </c>
+      <c r="O17" s="3" t="inlineStr">
+        <is>
+          <t>60–85</t>
+        </is>
+      </c>
+      <c r="P17" s="3" t="n">
+        <v>35</v>
+      </c>
+      <c r="Q17" s="3" t="n">
+        <v>295</v>
+      </c>
+      <c r="R17" s="3" t="n">
+        <v>206</v>
+      </c>
+      <c r="S17" s="3" t="n">
+        <v>59</v>
+      </c>
+      <c r="T17" s="3" t="n">
+        <v>30</v>
+      </c>
+      <c r="U17" s="3" t="n">
+        <v>35</v>
+      </c>
+      <c r="V17" s="3" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="3" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="C18" s="3" t="n">
+        <v>44</v>
+      </c>
+      <c r="D18" s="3" t="n">
+        <v>76</v>
+      </c>
+      <c r="E18" s="3" t="n">
+        <v>12</v>
+      </c>
+      <c r="F18" s="3" t="n">
+        <v>132</v>
+      </c>
+      <c r="G18" s="3" t="n">
+        <v>80</v>
+      </c>
+      <c r="H18" s="3" t="n">
+        <v>40</v>
+      </c>
+      <c r="I18" s="3" t="n">
+        <v>320</v>
+      </c>
+      <c r="J18" s="3" t="n">
+        <v>10400</v>
+      </c>
+      <c r="K18" s="5" t="n">
+        <v>0.1016949152542372</v>
+      </c>
+      <c r="L18" s="3" t="n">
+        <v>536</v>
+      </c>
+      <c r="M18" s="3" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="N18" s="3" t="n">
+        <v>25.2</v>
+      </c>
+      <c r="O18" s="3" t="inlineStr">
+        <is>
+          <t>65–95</t>
+        </is>
+      </c>
+      <c r="P18" s="3" t="n">
+        <v>35</v>
+      </c>
+      <c r="Q18" s="3" t="n">
+        <v>355</v>
+      </c>
+      <c r="R18" s="3" t="n">
+        <v>248</v>
+      </c>
+      <c r="S18" s="3" t="n">
+        <v>71</v>
+      </c>
+      <c r="T18" s="3" t="n">
+        <v>36</v>
+      </c>
+      <c r="U18" s="3" t="n">
+        <v>35</v>
+      </c>
+      <c r="V18" s="3" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="3" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="C19" s="3" t="n">
+        <v>48</v>
+      </c>
+      <c r="D19" s="3" t="n">
+        <v>84</v>
+      </c>
+      <c r="E19" s="3" t="n">
+        <v>14</v>
+      </c>
+      <c r="F19" s="3" t="n">
+        <v>146</v>
+      </c>
+      <c r="G19" s="3" t="n">
+        <v>80</v>
+      </c>
+      <c r="H19" s="3" t="n">
+        <v>40</v>
+      </c>
+      <c r="I19" s="3" t="n">
+        <v>320</v>
+      </c>
+      <c r="J19" s="3" t="n">
+        <v>11680</v>
+      </c>
+      <c r="K19" s="5" t="n">
+        <v>0.1230769230769231</v>
+      </c>
+      <c r="L19" s="3" t="n">
+        <v>604</v>
+      </c>
+      <c r="M19" s="3" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="N19" s="3" t="n">
+        <v>21.5</v>
+      </c>
+      <c r="O19" s="3" t="inlineStr">
+        <is>
+          <t>70–105</t>
+        </is>
+      </c>
+      <c r="P19" s="3" t="n">
+        <v>35</v>
+      </c>
+      <c r="Q19" s="3" t="n">
+        <v>430</v>
+      </c>
+      <c r="R19" s="3" t="n">
+        <v>301</v>
+      </c>
+      <c r="S19" s="3" t="n">
+        <v>86</v>
+      </c>
+      <c r="T19" s="3" t="n">
+        <v>43</v>
+      </c>
+      <c r="U19" s="3" t="n">
+        <v>35</v>
+      </c>
+      <c r="V19" s="3" t="inlineStr">
+        <is>
+          <t>模块Draft</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="3" t="n">
+        <v>19</v>
+      </c>
+      <c r="B20" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="C20" s="3" t="n">
+        <v>52</v>
+      </c>
+      <c r="D20" s="3" t="n">
+        <v>92</v>
+      </c>
+      <c r="E20" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="F20" s="3" t="n">
+        <v>160</v>
+      </c>
+      <c r="G20" s="3" t="n">
+        <v>80</v>
+      </c>
+      <c r="H20" s="3" t="n">
+        <v>40</v>
+      </c>
+      <c r="I20" s="3" t="n">
+        <v>320</v>
+      </c>
+      <c r="J20" s="3" t="n">
+        <v>12960</v>
+      </c>
+      <c r="K20" s="5" t="n">
+        <v>0.1095890410958904</v>
+      </c>
+      <c r="L20" s="3" t="n">
+        <v>672</v>
+      </c>
+      <c r="M20" s="3" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="N20" s="3" t="n">
+        <v>17.7</v>
+      </c>
+      <c r="O20" s="3" t="inlineStr">
+        <is>
+          <t>75–115</t>
+        </is>
+      </c>
+      <c r="P20" s="3" t="n">
+        <v>35</v>
+      </c>
+      <c r="Q20" s="3" t="n">
+        <v>515</v>
+      </c>
+      <c r="R20" s="3" t="n">
+        <v>360</v>
+      </c>
+      <c r="S20" s="3" t="n">
+        <v>103</v>
+      </c>
+      <c r="T20" s="3" t="n">
+        <v>52</v>
+      </c>
+      <c r="U20" s="3" t="n">
+        <v>35</v>
+      </c>
+      <c r="V20" s="3" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="3" t="n">
+        <v>20</v>
+      </c>
+      <c r="B21" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="C21" s="3" t="n">
+        <v>58</v>
+      </c>
+      <c r="D21" s="3" t="n">
+        <v>104</v>
+      </c>
+      <c r="E21" s="3" t="n">
+        <v>18</v>
+      </c>
+      <c r="F21" s="3" t="n">
+        <v>180</v>
+      </c>
+      <c r="G21" s="3" t="n">
+        <v>80</v>
+      </c>
+      <c r="H21" s="3" t="n">
+        <v>40</v>
+      </c>
+      <c r="I21" s="3" t="n">
+        <v>320</v>
+      </c>
+      <c r="J21" s="3" t="n">
+        <v>14560</v>
+      </c>
+      <c r="K21" s="5" t="n">
+        <v>0.1234567901234569</v>
+      </c>
+      <c r="L21" s="3" t="n">
+        <v>754</v>
+      </c>
+      <c r="M21" s="3" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="N21" s="3" t="n">
+        <v>13.2</v>
+      </c>
+      <c r="O21" s="3" t="inlineStr">
+        <is>
+          <t>80–130</t>
+        </is>
+      </c>
+      <c r="P21" s="3" t="n">
+        <v>50</v>
+      </c>
+      <c r="Q21" s="3" t="n">
+        <v>620</v>
+      </c>
+      <c r="R21" s="3" t="n">
+        <v>434</v>
+      </c>
+      <c r="S21" s="3" t="n">
+        <v>124</v>
+      </c>
+      <c r="T21" s="3" t="n">
+        <v>62</v>
+      </c>
+      <c r="U21" s="3" t="n">
+        <v>35</v>
+      </c>
+      <c r="V21" s="3" t="inlineStr">
+        <is>
+          <t>发射器+祝福束缚</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="3" t="n">
+        <v>21</v>
+      </c>
+      <c r="B22" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="C22" s="3" t="n">
+        <v>62</v>
+      </c>
+      <c r="D22" s="3" t="n">
+        <v>112</v>
+      </c>
+      <c r="E22" s="3" t="n">
+        <v>20</v>
+      </c>
+      <c r="F22" s="3" t="n">
+        <v>194</v>
+      </c>
+      <c r="G22" s="3" t="n">
+        <v>130</v>
+      </c>
+      <c r="H22" s="3" t="n">
+        <v>65</v>
+      </c>
+      <c r="I22" s="3" t="n">
+        <v>520</v>
+      </c>
+      <c r="J22" s="3" t="n">
+        <v>25740</v>
+      </c>
+      <c r="K22" s="5" t="n">
+        <v>0.7678571428571428</v>
+      </c>
+      <c r="L22" s="3" t="n">
+        <v>822</v>
+      </c>
+      <c r="M22" s="3" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="N22" s="3" t="n">
+        <v>40</v>
+      </c>
+      <c r="O22" s="3" t="inlineStr">
+        <is>
+          <t>90–145</t>
+        </is>
+      </c>
+      <c r="P22" s="3" t="n">
+        <v>45</v>
+      </c>
+      <c r="Q22" s="3" t="n">
+        <v>750</v>
+      </c>
+      <c r="R22" s="3" t="n">
+        <v>525</v>
+      </c>
+      <c r="S22" s="3" t="n">
+        <v>150</v>
+      </c>
+      <c r="T22" s="3" t="n">
+        <v>75</v>
+      </c>
+      <c r="U22" s="3" t="n">
+        <v>49</v>
+      </c>
+      <c r="V22" s="3" t="inlineStr">
+        <is>
+          <t>模块Draft</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="3" t="n">
+        <v>22</v>
+      </c>
+      <c r="B23" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="C23" s="3" t="n">
+        <v>66</v>
+      </c>
+      <c r="D23" s="3" t="n">
+        <v>120</v>
+      </c>
+      <c r="E23" s="3" t="n">
+        <v>22</v>
+      </c>
+      <c r="F23" s="3" t="n">
+        <v>208</v>
+      </c>
+      <c r="G23" s="3" t="n">
+        <v>130</v>
+      </c>
+      <c r="H23" s="3" t="n">
+        <v>65</v>
+      </c>
+      <c r="I23" s="3" t="n">
+        <v>520</v>
+      </c>
+      <c r="J23" s="3" t="n">
+        <v>27820</v>
+      </c>
+      <c r="K23" s="5" t="n">
+        <v>0.08080808080808088</v>
+      </c>
+      <c r="L23" s="3" t="n">
+        <v>890</v>
+      </c>
+      <c r="M23" s="3" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="N23" s="3" t="n">
+        <v>33.7</v>
+      </c>
+      <c r="O23" s="3" t="inlineStr">
+        <is>
+          <t>100–160</t>
+        </is>
+      </c>
+      <c r="P23" s="3" t="n">
+        <v>45</v>
+      </c>
+      <c r="Q23" s="3" t="n">
+        <v>905</v>
+      </c>
+      <c r="R23" s="3" t="n">
+        <v>634</v>
+      </c>
+      <c r="S23" s="3" t="n">
+        <v>181</v>
+      </c>
+      <c r="T23" s="3" t="n">
+        <v>90</v>
+      </c>
+      <c r="U23" s="3" t="n">
+        <v>49</v>
+      </c>
+      <c r="V23" s="3" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="3" t="n">
+        <v>23</v>
+      </c>
+      <c r="B24" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="C24" s="3" t="n">
+        <v>72</v>
+      </c>
+      <c r="D24" s="3" t="n">
+        <v>130</v>
+      </c>
+      <c r="E24" s="3" t="n">
+        <v>24</v>
+      </c>
+      <c r="F24" s="3" t="n">
+        <v>226</v>
+      </c>
+      <c r="G24" s="3" t="n">
+        <v>130</v>
+      </c>
+      <c r="H24" s="3" t="n">
+        <v>65</v>
+      </c>
+      <c r="I24" s="3" t="n">
+        <v>520</v>
+      </c>
+      <c r="J24" s="3" t="n">
+        <v>30290</v>
+      </c>
+      <c r="K24" s="5" t="n">
+        <v>0.08878504672897192</v>
+      </c>
+      <c r="L24" s="3" t="n">
+        <v>970</v>
+      </c>
+      <c r="M24" s="3" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="N24" s="3" t="n">
+        <v>26.7</v>
+      </c>
+      <c r="O24" s="3" t="inlineStr">
+        <is>
+          <t>110–175</t>
+        </is>
+      </c>
+      <c r="P24" s="3" t="n">
+        <v>45</v>
+      </c>
+      <c r="Q24" s="3" t="n">
+        <v>1090</v>
+      </c>
+      <c r="R24" s="3" t="n">
+        <v>763</v>
+      </c>
+      <c r="S24" s="3" t="n">
+        <v>218</v>
+      </c>
+      <c r="T24" s="3" t="n">
+        <v>109</v>
+      </c>
+      <c r="U24" s="3" t="n">
+        <v>49</v>
+      </c>
+      <c r="V24" s="3" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="3" t="n">
+        <v>24</v>
+      </c>
+      <c r="B25" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="C25" s="3" t="n">
+        <v>78</v>
+      </c>
+      <c r="D25" s="3" t="n">
+        <v>140</v>
+      </c>
+      <c r="E25" s="3" t="n">
+        <v>26</v>
+      </c>
+      <c r="F25" s="3" t="n">
+        <v>244</v>
+      </c>
+      <c r="G25" s="3" t="n">
+        <v>130</v>
+      </c>
+      <c r="H25" s="3" t="n">
+        <v>65</v>
+      </c>
+      <c r="I25" s="3" t="n">
+        <v>520</v>
+      </c>
+      <c r="J25" s="3" t="n">
+        <v>32760</v>
+      </c>
+      <c r="K25" s="5" t="n">
+        <v>0.0815450643776825</v>
+      </c>
+      <c r="L25" s="3" t="n">
+        <v>1050</v>
+      </c>
+      <c r="M25" s="3" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="N25" s="3" t="n">
+        <v>21.6</v>
+      </c>
+      <c r="O25" s="3" t="inlineStr">
+        <is>
+          <t>120–190</t>
+        </is>
+      </c>
+      <c r="P25" s="3" t="n">
+        <v>45</v>
+      </c>
+      <c r="Q25" s="3" t="n">
+        <v>1310</v>
+      </c>
+      <c r="R25" s="3" t="n">
+        <v>917</v>
+      </c>
+      <c r="S25" s="3" t="n">
+        <v>262</v>
+      </c>
+      <c r="T25" s="3" t="n">
+        <v>131</v>
+      </c>
+      <c r="U25" s="3" t="n">
+        <v>49</v>
+      </c>
+      <c r="V25" s="3" t="inlineStr">
+        <is>
+          <t>模块Draft</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="3" t="n">
+        <v>25</v>
+      </c>
+      <c r="B26" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="C26" s="3" t="n">
+        <v>88</v>
+      </c>
+      <c r="D26" s="3" t="n">
+        <v>160</v>
+      </c>
+      <c r="E26" s="3" t="n">
+        <v>30</v>
+      </c>
+      <c r="F26" s="3" t="n">
+        <v>278</v>
+      </c>
+      <c r="G26" s="3" t="n">
+        <v>130</v>
+      </c>
+      <c r="H26" s="3" t="n">
+        <v>65</v>
+      </c>
+      <c r="I26" s="3" t="n">
+        <v>520</v>
+      </c>
+      <c r="J26" s="3" t="n">
+        <v>37440</v>
+      </c>
+      <c r="K26" s="5" t="n">
+        <v>0.1428571428571428</v>
+      </c>
+      <c r="L26" s="3" t="n">
+        <v>1200</v>
+      </c>
+      <c r="M26" s="3" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="N26" s="3" t="n">
+        <v>16.4</v>
+      </c>
+      <c r="O26" s="3" t="inlineStr">
+        <is>
+          <t>130–210</t>
+        </is>
+      </c>
+      <c r="P26" s="3" t="n">
+        <v>60</v>
+      </c>
+      <c r="Q26" s="3" t="n">
+        <v>1580</v>
+      </c>
+      <c r="R26" s="3" t="n">
+        <v>1106</v>
+      </c>
+      <c r="S26" s="3" t="n">
+        <v>316</v>
+      </c>
+      <c r="T26" s="3" t="n">
+        <v>158</v>
+      </c>
+      <c r="U26" s="3" t="n">
+        <v>49</v>
+      </c>
+      <c r="V26" s="3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1960,7 +2672,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K20"/>
+  <dimension ref="A1:O25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -1974,6 +2686,10 @@
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
+    <col width="10" customWidth="1" min="12" max="12"/>
+    <col width="10" customWidth="1" min="13" max="13"/>
+    <col width="10" customWidth="1" min="14" max="14"/>
+    <col width="10" customWidth="1" min="15" max="15"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2032,6 +2748,26 @@
           <t>波15价</t>
         </is>
       </c>
+      <c r="L1" s="2" t="inlineStr">
+        <is>
+          <t>波16价</t>
+        </is>
+      </c>
+      <c r="M1" s="2" t="inlineStr">
+        <is>
+          <t>波20价</t>
+        </is>
+      </c>
+      <c r="N1" s="2" t="inlineStr">
+        <is>
+          <t>波21价</t>
+        </is>
+      </c>
+      <c r="O1" s="2" t="inlineStr">
+        <is>
+          <t>波25价</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
@@ -2069,6 +2805,18 @@
       <c r="K2" s="3" t="n">
         <v>65</v>
       </c>
+      <c r="L2" s="3" t="n">
+        <v>115</v>
+      </c>
+      <c r="M2" s="3" t="n">
+        <v>115</v>
+      </c>
+      <c r="N2" s="3" t="n">
+        <v>210</v>
+      </c>
+      <c r="O2" s="3" t="n">
+        <v>210</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
@@ -2106,6 +2854,18 @@
       <c r="K3" s="3" t="n">
         <v>145</v>
       </c>
+      <c r="L3" s="3" t="n">
+        <v>260</v>
+      </c>
+      <c r="M3" s="3" t="n">
+        <v>260</v>
+      </c>
+      <c r="N3" s="3" t="n">
+        <v>470</v>
+      </c>
+      <c r="O3" s="3" t="n">
+        <v>470</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
@@ -2143,6 +2903,18 @@
       <c r="K4" s="3" t="n">
         <v>330</v>
       </c>
+      <c r="L4" s="3" t="n">
+        <v>590</v>
+      </c>
+      <c r="M4" s="3" t="n">
+        <v>590</v>
+      </c>
+      <c r="N4" s="3" t="n">
+        <v>1065</v>
+      </c>
+      <c r="O4" s="3" t="n">
+        <v>1065</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
@@ -2180,6 +2952,18 @@
       <c r="K5" s="3" t="n">
         <v>740</v>
       </c>
+      <c r="L5" s="3" t="n">
+        <v>1330</v>
+      </c>
+      <c r="M5" s="3" t="n">
+        <v>1330</v>
+      </c>
+      <c r="N5" s="3" t="n">
+        <v>2390</v>
+      </c>
+      <c r="O5" s="3" t="n">
+        <v>2390</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
@@ -2217,6 +3001,18 @@
       <c r="K6" s="3" t="n">
         <v>1660</v>
       </c>
+      <c r="L6" s="3" t="n">
+        <v>2990</v>
+      </c>
+      <c r="M6" s="3" t="n">
+        <v>2990</v>
+      </c>
+      <c r="N6" s="3" t="n">
+        <v>5380</v>
+      </c>
+      <c r="O6" s="3" t="n">
+        <v>5380</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
@@ -2254,6 +3050,18 @@
       <c r="K7" s="3" t="n">
         <v>80</v>
       </c>
+      <c r="L7" s="3" t="n">
+        <v>145</v>
+      </c>
+      <c r="M7" s="3" t="n">
+        <v>145</v>
+      </c>
+      <c r="N7" s="3" t="n">
+        <v>260</v>
+      </c>
+      <c r="O7" s="3" t="n">
+        <v>260</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
@@ -2291,6 +3099,18 @@
       <c r="K8" s="3" t="n">
         <v>180</v>
       </c>
+      <c r="L8" s="3" t="n">
+        <v>330</v>
+      </c>
+      <c r="M8" s="3" t="n">
+        <v>330</v>
+      </c>
+      <c r="N8" s="3" t="n">
+        <v>590</v>
+      </c>
+      <c r="O8" s="3" t="n">
+        <v>590</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
@@ -2328,6 +3148,18 @@
       <c r="K9" s="3" t="n">
         <v>410</v>
       </c>
+      <c r="L9" s="3" t="n">
+        <v>740</v>
+      </c>
+      <c r="M9" s="3" t="n">
+        <v>740</v>
+      </c>
+      <c r="N9" s="3" t="n">
+        <v>1330</v>
+      </c>
+      <c r="O9" s="3" t="n">
+        <v>1330</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
@@ -2365,6 +3197,18 @@
       <c r="K10" s="3" t="n">
         <v>925</v>
       </c>
+      <c r="L10" s="3" t="n">
+        <v>1660</v>
+      </c>
+      <c r="M10" s="3" t="n">
+        <v>1660</v>
+      </c>
+      <c r="N10" s="3" t="n">
+        <v>2990</v>
+      </c>
+      <c r="O10" s="3" t="n">
+        <v>2990</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
@@ -2402,6 +3246,18 @@
       <c r="K11" s="3" t="n">
         <v>2075</v>
       </c>
+      <c r="L11" s="3" t="n">
+        <v>3735</v>
+      </c>
+      <c r="M11" s="3" t="n">
+        <v>3735</v>
+      </c>
+      <c r="N11" s="3" t="n">
+        <v>6725</v>
+      </c>
+      <c r="O11" s="3" t="n">
+        <v>6725</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
@@ -2439,6 +3295,18 @@
       <c r="K12" s="3" t="n">
         <v>70</v>
       </c>
+      <c r="L12" s="3" t="n">
+        <v>130</v>
+      </c>
+      <c r="M12" s="3" t="n">
+        <v>130</v>
+      </c>
+      <c r="N12" s="3" t="n">
+        <v>230</v>
+      </c>
+      <c r="O12" s="3" t="n">
+        <v>230</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
@@ -2476,6 +3344,18 @@
       <c r="K13" s="3" t="n">
         <v>160</v>
       </c>
+      <c r="L13" s="3" t="n">
+        <v>290</v>
+      </c>
+      <c r="M13" s="3" t="n">
+        <v>290</v>
+      </c>
+      <c r="N13" s="3" t="n">
+        <v>520</v>
+      </c>
+      <c r="O13" s="3" t="n">
+        <v>520</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
@@ -2513,6 +3393,18 @@
       <c r="K14" s="3" t="n">
         <v>360</v>
       </c>
+      <c r="L14" s="3" t="n">
+        <v>650</v>
+      </c>
+      <c r="M14" s="3" t="n">
+        <v>650</v>
+      </c>
+      <c r="N14" s="3" t="n">
+        <v>1170</v>
+      </c>
+      <c r="O14" s="3" t="n">
+        <v>1170</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
@@ -2550,6 +3442,18 @@
       <c r="K15" s="3" t="n">
         <v>810</v>
       </c>
+      <c r="L15" s="3" t="n">
+        <v>1460</v>
+      </c>
+      <c r="M15" s="3" t="n">
+        <v>1460</v>
+      </c>
+      <c r="N15" s="3" t="n">
+        <v>2630</v>
+      </c>
+      <c r="O15" s="3" t="n">
+        <v>2630</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
@@ -2587,153 +3491,458 @@
       <c r="K16" s="3" t="n">
         <v>1825</v>
       </c>
+      <c r="L16" s="3" t="n">
+        <v>3290</v>
+      </c>
+      <c r="M16" s="3" t="n">
+        <v>3290</v>
+      </c>
+      <c r="N16" s="3" t="n">
+        <v>5920</v>
+      </c>
+      <c r="O16" s="3" t="n">
+        <v>5920</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>比特币采矿机</t>
+          <t>黑洞发射器</t>
         </is>
       </c>
       <c r="B17" s="3" t="n">
         <v>1</v>
       </c>
       <c r="C17" s="3" t="n">
-        <v>20</v>
+        <v>110</v>
       </c>
       <c r="D17" s="3" t="n">
-        <v>20</v>
+        <v>110</v>
       </c>
       <c r="E17" s="3" t="n">
-        <v>20</v>
+        <v>110</v>
       </c>
       <c r="F17" s="3" t="n">
-        <v>30</v>
+        <v>200</v>
       </c>
       <c r="G17" s="3" t="n">
-        <v>30</v>
+        <v>200</v>
       </c>
       <c r="H17" s="3" t="n">
-        <v>30</v>
+        <v>200</v>
       </c>
       <c r="I17" s="3" t="n">
-        <v>60</v>
+        <v>365</v>
       </c>
       <c r="J17" s="3" t="n">
-        <v>60</v>
+        <v>365</v>
       </c>
       <c r="K17" s="3" t="n">
-        <v>60</v>
+        <v>365</v>
+      </c>
+      <c r="L17" s="3" t="n">
+        <v>655</v>
+      </c>
+      <c r="M17" s="3" t="n">
+        <v>655</v>
+      </c>
+      <c r="N17" s="3" t="n">
+        <v>1180</v>
+      </c>
+      <c r="O17" s="3" t="n">
+        <v>1180</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="3" t="inlineStr">
         <is>
-          <t>比特币采矿机</t>
+          <t>黑洞发射器</t>
         </is>
       </c>
       <c r="B18" s="3" t="n">
         <v>2</v>
       </c>
       <c r="C18" s="3" t="n">
-        <v>25</v>
+        <v>290</v>
       </c>
       <c r="D18" s="3" t="n">
-        <v>25</v>
+        <v>290</v>
       </c>
       <c r="E18" s="3" t="n">
-        <v>25</v>
+        <v>290</v>
       </c>
       <c r="F18" s="3" t="n">
-        <v>45</v>
+        <v>525</v>
       </c>
       <c r="G18" s="3" t="n">
-        <v>45</v>
+        <v>525</v>
       </c>
       <c r="H18" s="3" t="n">
-        <v>45</v>
+        <v>525</v>
       </c>
       <c r="I18" s="3" t="n">
-        <v>80</v>
+        <v>950</v>
       </c>
       <c r="J18" s="3" t="n">
-        <v>80</v>
+        <v>950</v>
       </c>
       <c r="K18" s="3" t="n">
-        <v>80</v>
+        <v>950</v>
+      </c>
+      <c r="L18" s="3" t="n">
+        <v>1705</v>
+      </c>
+      <c r="M18" s="3" t="n">
+        <v>1705</v>
+      </c>
+      <c r="N18" s="3" t="n">
+        <v>3070</v>
+      </c>
+      <c r="O18" s="3" t="n">
+        <v>3070</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>比特币采矿机</t>
+          <t>黑洞发射器</t>
         </is>
       </c>
       <c r="B19" s="3" t="n">
         <v>3</v>
       </c>
       <c r="C19" s="3" t="n">
-        <v>30</v>
+        <v>760</v>
       </c>
       <c r="D19" s="3" t="n">
-        <v>30</v>
+        <v>760</v>
       </c>
       <c r="E19" s="3" t="n">
-        <v>30</v>
+        <v>760</v>
       </c>
       <c r="F19" s="3" t="n">
-        <v>55</v>
+        <v>1370</v>
       </c>
       <c r="G19" s="3" t="n">
-        <v>55</v>
+        <v>1370</v>
       </c>
       <c r="H19" s="3" t="n">
-        <v>55</v>
+        <v>1370</v>
       </c>
       <c r="I19" s="3" t="n">
-        <v>100</v>
+        <v>2465</v>
       </c>
       <c r="J19" s="3" t="n">
-        <v>100</v>
+        <v>2465</v>
       </c>
       <c r="K19" s="3" t="n">
-        <v>100</v>
+        <v>2465</v>
+      </c>
+      <c r="L19" s="3" t="n">
+        <v>4435</v>
+      </c>
+      <c r="M19" s="3" t="n">
+        <v>4435</v>
+      </c>
+      <c r="N19" s="3" t="n">
+        <v>7985</v>
+      </c>
+      <c r="O19" s="3" t="n">
+        <v>7985</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="3" t="inlineStr">
         <is>
+          <t>黑洞发射器</t>
+        </is>
+      </c>
+      <c r="B20" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="C20" s="3" t="n">
+        <v>1975</v>
+      </c>
+      <c r="D20" s="3" t="n">
+        <v>1975</v>
+      </c>
+      <c r="E20" s="3" t="n">
+        <v>1975</v>
+      </c>
+      <c r="F20" s="3" t="n">
+        <v>3560</v>
+      </c>
+      <c r="G20" s="3" t="n">
+        <v>3560</v>
+      </c>
+      <c r="H20" s="3" t="n">
+        <v>3560</v>
+      </c>
+      <c r="I20" s="3" t="n">
+        <v>6405</v>
+      </c>
+      <c r="J20" s="3" t="n">
+        <v>6405</v>
+      </c>
+      <c r="K20" s="3" t="n">
+        <v>6405</v>
+      </c>
+      <c r="L20" s="3" t="n">
+        <v>11530</v>
+      </c>
+      <c r="M20" s="3" t="n">
+        <v>11530</v>
+      </c>
+      <c r="N20" s="3" t="n">
+        <v>20755</v>
+      </c>
+      <c r="O20" s="3" t="n">
+        <v>20755</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="3" t="inlineStr">
+        <is>
+          <t>黑洞发射器</t>
+        </is>
+      </c>
+      <c r="B21" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="C21" s="3" t="n">
+        <v>5140</v>
+      </c>
+      <c r="D21" s="3" t="n">
+        <v>5140</v>
+      </c>
+      <c r="E21" s="3" t="n">
+        <v>5140</v>
+      </c>
+      <c r="F21" s="3" t="n">
+        <v>9255</v>
+      </c>
+      <c r="G21" s="3" t="n">
+        <v>9255</v>
+      </c>
+      <c r="H21" s="3" t="n">
+        <v>9255</v>
+      </c>
+      <c r="I21" s="3" t="n">
+        <v>16655</v>
+      </c>
+      <c r="J21" s="3" t="n">
+        <v>16655</v>
+      </c>
+      <c r="K21" s="3" t="n">
+        <v>16655</v>
+      </c>
+      <c r="L21" s="3" t="n">
+        <v>29980</v>
+      </c>
+      <c r="M21" s="3" t="n">
+        <v>29980</v>
+      </c>
+      <c r="N21" s="3" t="n">
+        <v>53970</v>
+      </c>
+      <c r="O21" s="3" t="n">
+        <v>53970</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="3" t="inlineStr">
+        <is>
+          <t>比特币采矿机</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C22" s="3" t="n">
+        <v>25</v>
+      </c>
+      <c r="D22" s="3" t="n">
+        <v>25</v>
+      </c>
+      <c r="E22" s="3" t="n">
+        <v>25</v>
+      </c>
+      <c r="F22" s="3" t="n">
+        <v>50</v>
+      </c>
+      <c r="G22" s="3" t="n">
+        <v>50</v>
+      </c>
+      <c r="H22" s="3" t="n">
+        <v>50</v>
+      </c>
+      <c r="I22" s="3" t="n">
+        <v>85</v>
+      </c>
+      <c r="J22" s="3" t="n">
+        <v>85</v>
+      </c>
+      <c r="K22" s="3" t="n">
+        <v>85</v>
+      </c>
+      <c r="L22" s="3" t="n">
+        <v>155</v>
+      </c>
+      <c r="M22" s="3" t="n">
+        <v>155</v>
+      </c>
+      <c r="N22" s="3" t="n">
+        <v>285</v>
+      </c>
+      <c r="O22" s="3" t="n">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="3" t="inlineStr">
+        <is>
+          <t>比特币采矿机</t>
+        </is>
+      </c>
+      <c r="B23" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="C23" s="3" t="n">
+        <v>35</v>
+      </c>
+      <c r="D23" s="3" t="n">
+        <v>35</v>
+      </c>
+      <c r="E23" s="3" t="n">
+        <v>35</v>
+      </c>
+      <c r="F23" s="3" t="n">
+        <v>65</v>
+      </c>
+      <c r="G23" s="3" t="n">
+        <v>65</v>
+      </c>
+      <c r="H23" s="3" t="n">
+        <v>65</v>
+      </c>
+      <c r="I23" s="3" t="n">
+        <v>120</v>
+      </c>
+      <c r="J23" s="3" t="n">
+        <v>120</v>
+      </c>
+      <c r="K23" s="3" t="n">
+        <v>120</v>
+      </c>
+      <c r="L23" s="3" t="n">
+        <v>215</v>
+      </c>
+      <c r="M23" s="3" t="n">
+        <v>215</v>
+      </c>
+      <c r="N23" s="3" t="n">
+        <v>385</v>
+      </c>
+      <c r="O23" s="3" t="n">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="3" t="inlineStr">
+        <is>
+          <t>比特币采矿机</t>
+        </is>
+      </c>
+      <c r="B24" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="C24" s="3" t="n">
+        <v>45</v>
+      </c>
+      <c r="D24" s="3" t="n">
+        <v>45</v>
+      </c>
+      <c r="E24" s="3" t="n">
+        <v>45</v>
+      </c>
+      <c r="F24" s="3" t="n">
+        <v>85</v>
+      </c>
+      <c r="G24" s="3" t="n">
+        <v>85</v>
+      </c>
+      <c r="H24" s="3" t="n">
+        <v>85</v>
+      </c>
+      <c r="I24" s="3" t="n">
+        <v>150</v>
+      </c>
+      <c r="J24" s="3" t="n">
+        <v>150</v>
+      </c>
+      <c r="K24" s="3" t="n">
+        <v>150</v>
+      </c>
+      <c r="L24" s="3" t="n">
+        <v>270</v>
+      </c>
+      <c r="M24" s="3" t="n">
+        <v>270</v>
+      </c>
+      <c r="N24" s="3" t="n">
+        <v>480</v>
+      </c>
+      <c r="O24" s="3" t="n">
+        <v>480</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="3" t="inlineStr">
+        <is>
           <t>收束器</t>
         </is>
       </c>
-      <c r="B20" s="3" t="n">
+      <c r="B25" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="C20" s="3" t="n">
-        <v>15</v>
-      </c>
-      <c r="D20" s="3" t="n">
-        <v>15</v>
-      </c>
-      <c r="E20" s="3" t="n">
-        <v>15</v>
-      </c>
-      <c r="F20" s="3" t="n">
-        <v>25</v>
-      </c>
-      <c r="G20" s="3" t="n">
-        <v>25</v>
-      </c>
-      <c r="H20" s="3" t="n">
-        <v>25</v>
-      </c>
-      <c r="I20" s="3" t="n">
-        <v>50</v>
-      </c>
-      <c r="J20" s="3" t="n">
-        <v>50</v>
-      </c>
-      <c r="K20" s="3" t="n">
-        <v>50</v>
+      <c r="C25" s="3" t="n">
+        <v>20</v>
+      </c>
+      <c r="D25" s="3" t="n">
+        <v>20</v>
+      </c>
+      <c r="E25" s="3" t="n">
+        <v>20</v>
+      </c>
+      <c r="F25" s="3" t="n">
+        <v>40</v>
+      </c>
+      <c r="G25" s="3" t="n">
+        <v>40</v>
+      </c>
+      <c r="H25" s="3" t="n">
+        <v>40</v>
+      </c>
+      <c r="I25" s="3" t="n">
+        <v>75</v>
+      </c>
+      <c r="J25" s="3" t="n">
+        <v>75</v>
+      </c>
+      <c r="K25" s="3" t="n">
+        <v>75</v>
+      </c>
+      <c r="L25" s="3" t="n">
+        <v>130</v>
+      </c>
+      <c r="M25" s="3" t="n">
+        <v>130</v>
+      </c>
+      <c r="N25" s="3" t="n">
+        <v>235</v>
+      </c>
+      <c r="O25" s="3" t="n">
+        <v>235</v>
       </c>
     </row>
   </sheetData>
@@ -2798,22 +4007,22 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>波10混合HP</t>
+          <t>波15混合HP</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>波10清场秒(无环)</t>
+          <t>波15清场秒(无环)</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>波15混合HP</t>
+          <t>波25混合HP</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>波15清场秒(无环)</t>
+          <t>波25清场秒(无环)</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
@@ -2841,16 +4050,16 @@
         <v>2.5</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>1568</v>
+        <v>5300</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>627.2</v>
+        <v>2120</v>
       </c>
       <c r="H4" s="3" t="n">
-        <v>5300</v>
+        <v>37440</v>
       </c>
       <c r="I4" s="3" t="n">
-        <v>2120</v>
+        <v>14976</v>
       </c>
       <c r="J4" s="3" t="inlineStr">
         <is>
@@ -2877,16 +4086,16 @@
         <v>8</v>
       </c>
       <c r="F5" s="3" t="n">
-        <v>1568</v>
+        <v>5300</v>
       </c>
       <c r="G5" s="3" t="n">
-        <v>196</v>
+        <v>662.5</v>
       </c>
       <c r="H5" s="3" t="n">
-        <v>5300</v>
+        <v>37440</v>
       </c>
       <c r="I5" s="3" t="n">
-        <v>662.5</v>
+        <v>4680</v>
       </c>
       <c r="J5" s="3" t="inlineStr">
         <is>
@@ -2913,16 +4122,16 @@
         <v>26</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>1568</v>
+        <v>5300</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>60.3</v>
+        <v>203.8</v>
       </c>
       <c r="H6" s="3" t="n">
-        <v>5300</v>
+        <v>37440</v>
       </c>
       <c r="I6" s="3" t="n">
-        <v>203.8</v>
+        <v>1440</v>
       </c>
       <c r="J6" s="3" t="inlineStr">
         <is>
@@ -2949,16 +4158,16 @@
         <v>6.2</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>1568</v>
+        <v>5300</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>250.9</v>
+        <v>848</v>
       </c>
       <c r="H7" s="3" t="n">
-        <v>5300</v>
+        <v>37440</v>
       </c>
       <c r="I7" s="3" t="n">
-        <v>848</v>
+        <v>5990.4</v>
       </c>
       <c r="J7" s="3" t="inlineStr">
         <is>
@@ -2985,16 +4194,16 @@
         <v>20</v>
       </c>
       <c r="F8" s="3" t="n">
-        <v>1568</v>
+        <v>5300</v>
       </c>
       <c r="G8" s="3" t="n">
-        <v>78.40000000000001</v>
+        <v>265</v>
       </c>
       <c r="H8" s="3" t="n">
-        <v>5300</v>
+        <v>37440</v>
       </c>
       <c r="I8" s="3" t="n">
-        <v>265</v>
+        <v>1872</v>
       </c>
       <c r="J8" s="3" t="inlineStr">
         <is>
@@ -3021,16 +4230,16 @@
         <v>65</v>
       </c>
       <c r="F9" s="3" t="n">
-        <v>1568</v>
+        <v>5300</v>
       </c>
       <c r="G9" s="3" t="n">
-        <v>24.1</v>
+        <v>81.5</v>
       </c>
       <c r="H9" s="3" t="n">
-        <v>5300</v>
+        <v>37440</v>
       </c>
       <c r="I9" s="3" t="n">
-        <v>81.5</v>
+        <v>576</v>
       </c>
       <c r="J9" s="3" t="inlineStr">
         <is>
@@ -3045,7 +4254,7 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C10" s="3" t="n">
         <v>1</v>
@@ -3054,19 +4263,19 @@
         <v>5</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>1568</v>
+        <v>5300</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>62.7</v>
+        <v>530</v>
       </c>
       <c r="H10" s="3" t="n">
-        <v>5300</v>
+        <v>37440</v>
       </c>
       <c r="I10" s="3" t="n">
-        <v>212</v>
+        <v>3744</v>
       </c>
       <c r="J10" s="3" t="inlineStr">
         <is>
@@ -3081,7 +4290,7 @@
         </is>
       </c>
       <c r="B11" s="3" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C11" s="3" t="n">
         <v>3</v>
@@ -3090,19 +4299,19 @@
         <v>16</v>
       </c>
       <c r="E11" s="3" t="n">
-        <v>80</v>
+        <v>32</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>1568</v>
+        <v>5300</v>
       </c>
       <c r="G11" s="3" t="n">
-        <v>19.6</v>
+        <v>165.6</v>
       </c>
       <c r="H11" s="3" t="n">
-        <v>5300</v>
+        <v>37440</v>
       </c>
       <c r="I11" s="3" t="n">
-        <v>66.2</v>
+        <v>1170</v>
       </c>
       <c r="J11" s="3" t="inlineStr">
         <is>
@@ -3117,7 +4326,7 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C12" s="3" t="n">
         <v>5</v>
@@ -3126,19 +4335,19 @@
         <v>52</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>260</v>
+        <v>104</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>1568</v>
+        <v>5300</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>6</v>
+        <v>51</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>5300</v>
+        <v>37440</v>
       </c>
       <c r="I12" s="3" t="n">
-        <v>20.4</v>
+        <v>360</v>
       </c>
       <c r="J12" s="3" t="inlineStr">
         <is>
@@ -3149,11 +4358,11 @@
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>双满 1.25×10</t>
+          <t>双满 1.25×4</t>
         </is>
       </c>
       <c r="B13" s="3" t="n">
-        <v>12.5</v>
+        <v>5</v>
       </c>
       <c r="C13" s="3" t="n">
         <v>1</v>
@@ -3162,19 +4371,19 @@
         <v>5</v>
       </c>
       <c r="E13" s="3" t="n">
-        <v>62.5</v>
+        <v>25</v>
       </c>
       <c r="F13" s="3" t="n">
-        <v>1568</v>
+        <v>5300</v>
       </c>
       <c r="G13" s="3" t="n">
-        <v>25.1</v>
+        <v>212</v>
       </c>
       <c r="H13" s="3" t="n">
-        <v>5300</v>
+        <v>37440</v>
       </c>
       <c r="I13" s="3" t="n">
-        <v>84.8</v>
+        <v>1497.6</v>
       </c>
       <c r="J13" s="3" t="inlineStr">
         <is>
@@ -3185,11 +4394,11 @@
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>双满 1.25×10</t>
+          <t>双满 1.25×4</t>
         </is>
       </c>
       <c r="B14" s="3" t="n">
-        <v>12.5</v>
+        <v>5</v>
       </c>
       <c r="C14" s="3" t="n">
         <v>3</v>
@@ -3198,19 +4407,19 @@
         <v>16</v>
       </c>
       <c r="E14" s="3" t="n">
-        <v>200</v>
+        <v>80</v>
       </c>
       <c r="F14" s="3" t="n">
-        <v>1568</v>
+        <v>5300</v>
       </c>
       <c r="G14" s="3" t="n">
-        <v>7.8</v>
+        <v>66.2</v>
       </c>
       <c r="H14" s="3" t="n">
-        <v>5300</v>
+        <v>37440</v>
       </c>
       <c r="I14" s="3" t="n">
-        <v>26.5</v>
+        <v>468</v>
       </c>
       <c r="J14" s="3" t="inlineStr">
         <is>
@@ -3221,11 +4430,11 @@
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>双满 1.25×10</t>
+          <t>双满 1.25×4</t>
         </is>
       </c>
       <c r="B15" s="3" t="n">
-        <v>12.5</v>
+        <v>5</v>
       </c>
       <c r="C15" s="3" t="n">
         <v>5</v>
@@ -3234,19 +4443,19 @@
         <v>52</v>
       </c>
       <c r="E15" s="3" t="n">
-        <v>650</v>
+        <v>260</v>
       </c>
       <c r="F15" s="3" t="n">
-        <v>1568</v>
+        <v>5300</v>
       </c>
       <c r="G15" s="3" t="n">
-        <v>2.4</v>
+        <v>20.4</v>
       </c>
       <c r="H15" s="3" t="n">
-        <v>5300</v>
+        <v>37440</v>
       </c>
       <c r="I15" s="3" t="n">
-        <v>8.199999999999999</v>
+        <v>144</v>
       </c>
       <c r="J15" s="3" t="inlineStr">
         <is>
@@ -3513,7 +4722,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E40"/>
+  <dimension ref="A1:E81"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -3614,16 +4823,16 @@
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C5" s="3" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="D5" s="3" t="n">
         <v>0</v>
       </c>
       <c r="E5" s="3" t="n">
-        <v>5</v>
+        <v>14</v>
       </c>
     </row>
     <row r="6">
@@ -3633,16 +4842,16 @@
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C6" s="3" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="D6" s="3" t="n">
         <v>0</v>
       </c>
       <c r="E6" s="3" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
     </row>
     <row r="7">
@@ -3655,13 +4864,13 @@
         <v>2</v>
       </c>
       <c r="C7" s="3" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="D7" s="3" t="n">
         <v>0</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>17</v>
+        <v>5</v>
       </c>
     </row>
     <row r="8">
@@ -3671,16 +4880,16 @@
         </is>
       </c>
       <c r="B8" s="3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C8" s="3" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="D8" s="3" t="n">
         <v>0</v>
       </c>
       <c r="E8" s="3" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="9">
@@ -3690,16 +4899,16 @@
         </is>
       </c>
       <c r="B9" s="3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C9" s="3" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="D9" s="3" t="n">
         <v>0</v>
       </c>
       <c r="E9" s="3" t="n">
-        <v>22</v>
+        <v>17</v>
       </c>
     </row>
     <row r="10">
@@ -3709,140 +4918,140 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="D10" s="3" t="n">
         <v>0</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>40</v>
+        <v>31</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>收束器</t>
+          <t>激光</t>
         </is>
       </c>
       <c r="B11" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C11" s="3" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="D11" s="3" t="n">
         <v>0</v>
       </c>
       <c r="E11" s="3" t="n">
-        <v>1</v>
+        <v>56</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>收束器</t>
+          <t>激光</t>
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="D12" s="3" t="n">
         <v>0</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>收束器</t>
+          <t>激光</t>
         </is>
       </c>
       <c r="B13" s="3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C13" s="3" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="D13" s="3" t="n">
         <v>0</v>
       </c>
       <c r="E13" s="3" t="n">
-        <v>3</v>
+        <v>22</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>炸弹</t>
+          <t>激光</t>
         </is>
       </c>
       <c r="B14" s="3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C14" s="3" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="D14" s="3" t="n">
         <v>0</v>
       </c>
       <c r="E14" s="3" t="n">
-        <v>3</v>
+        <v>40</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>炸弹</t>
+          <t>激光</t>
         </is>
       </c>
       <c r="B15" s="3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C15" s="3" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="D15" s="3" t="n">
         <v>0</v>
       </c>
       <c r="E15" s="3" t="n">
-        <v>5</v>
+        <v>71</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
         <is>
-          <t>炸弹</t>
+          <t>激光</t>
         </is>
       </c>
       <c r="B16" s="3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C16" s="3" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="D16" s="3" t="n">
         <v>0</v>
       </c>
       <c r="E16" s="3" t="n">
-        <v>10</v>
+        <v>128</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>炸弹</t>
+          <t>收束器</t>
         </is>
       </c>
       <c r="B17" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C17" s="3" t="n">
         <v>5</v>
@@ -3851,17 +5060,17 @@
         <v>0</v>
       </c>
       <c r="E17" s="3" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="3" t="inlineStr">
         <is>
-          <t>炸弹</t>
+          <t>收束器</t>
         </is>
       </c>
       <c r="B18" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C18" s="3" t="n">
         <v>10</v>
@@ -3870,17 +5079,17 @@
         <v>0</v>
       </c>
       <c r="E18" s="3" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>炸弹</t>
+          <t>收束器</t>
         </is>
       </c>
       <c r="B19" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C19" s="3" t="n">
         <v>15</v>
@@ -3889,45 +5098,45 @@
         <v>0</v>
       </c>
       <c r="E19" s="3" t="n">
-        <v>22</v>
+        <v>4</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="3" t="inlineStr">
         <is>
-          <t>炸弹</t>
+          <t>收束器</t>
         </is>
       </c>
       <c r="B20" s="3" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C20" s="3" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="D20" s="3" t="n">
         <v>0</v>
       </c>
       <c r="E20" s="3" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>炸弹</t>
+          <t>收束器</t>
         </is>
       </c>
       <c r="B21" s="3" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C21" s="3" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="D21" s="3" t="n">
         <v>0</v>
       </c>
       <c r="E21" s="3" t="n">
-        <v>28</v>
+        <v>14</v>
       </c>
     </row>
     <row r="22">
@@ -3937,197 +5146,197 @@
         </is>
       </c>
       <c r="B22" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C22" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="D22" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E22" s="3" t="n">
         <v>3</v>
-      </c>
-      <c r="C22" s="3" t="n">
-        <v>15</v>
-      </c>
-      <c r="D22" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E22" s="3" t="n">
-        <v>49</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>寒冰</t>
+          <t>炸弹</t>
         </is>
       </c>
       <c r="B23" s="3" t="n">
         <v>1</v>
       </c>
       <c r="C23" s="3" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="D23" s="3" t="n">
         <v>0</v>
       </c>
       <c r="E23" s="3" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="3" t="inlineStr">
         <is>
-          <t>寒冰</t>
+          <t>炸弹</t>
         </is>
       </c>
       <c r="B24" s="3" t="n">
         <v>1</v>
       </c>
       <c r="C24" s="3" t="n">
+        <v>15</v>
+      </c>
+      <c r="D24" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E24" s="3" t="n">
         <v>10</v>
-      </c>
-      <c r="D24" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E24" s="3" t="n">
-        <v>5</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t>寒冰</t>
+          <t>炸弹</t>
         </is>
       </c>
       <c r="B25" s="3" t="n">
         <v>1</v>
       </c>
       <c r="C25" s="3" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="D25" s="3" t="n">
         <v>0</v>
       </c>
       <c r="E25" s="3" t="n">
-        <v>8</v>
+        <v>17</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="inlineStr">
         <is>
-          <t>寒冰</t>
+          <t>炸弹</t>
         </is>
       </c>
       <c r="B26" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C26" s="3" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="D26" s="3" t="n">
         <v>0</v>
       </c>
       <c r="E26" s="3" t="n">
-        <v>6</v>
+        <v>31</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="inlineStr">
         <is>
-          <t>寒冰</t>
+          <t>炸弹</t>
         </is>
       </c>
       <c r="B27" s="3" t="n">
         <v>2</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="D27" s="3" t="n">
         <v>0</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>寒冰</t>
+          <t>炸弹</t>
         </is>
       </c>
       <c r="B28" s="3" t="n">
         <v>2</v>
       </c>
       <c r="C28" s="3" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="D28" s="3" t="n">
         <v>0</v>
       </c>
       <c r="E28" s="3" t="n">
-        <v>19</v>
+        <v>12</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t>寒冰</t>
+          <t>炸弹</t>
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="D29" s="3" t="n">
         <v>0</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>13</v>
+        <v>22</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="inlineStr">
         <is>
-          <t>寒冰</t>
+          <t>炸弹</t>
         </is>
       </c>
       <c r="B30" s="3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C30" s="3" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="D30" s="3" t="n">
         <v>0</v>
       </c>
       <c r="E30" s="3" t="n">
-        <v>24</v>
+        <v>40</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="inlineStr">
         <is>
-          <t>寒冰</t>
+          <t>炸弹</t>
         </is>
       </c>
       <c r="B31" s="3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C31" s="3" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="D31" s="3" t="n">
         <v>0</v>
       </c>
       <c r="E31" s="3" t="n">
-        <v>43</v>
+        <v>71</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="inlineStr">
         <is>
-          <t>采矿</t>
+          <t>炸弹</t>
         </is>
       </c>
       <c r="B32" s="3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C32" s="3" t="n">
         <v>5</v>
@@ -4136,17 +5345,17 @@
         <v>0</v>
       </c>
       <c r="E32" s="3" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="inlineStr">
         <is>
-          <t>采矿</t>
+          <t>炸弹</t>
         </is>
       </c>
       <c r="B33" s="3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C33" s="3" t="n">
         <v>10</v>
@@ -4155,17 +5364,17 @@
         <v>0</v>
       </c>
       <c r="E33" s="3" t="n">
-        <v>2</v>
+        <v>28</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="3" t="inlineStr">
         <is>
-          <t>采矿</t>
+          <t>炸弹</t>
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C34" s="3" t="n">
         <v>15</v>
@@ -4174,121 +5383,900 @@
         <v>0</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>4</v>
+        <v>49</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="3" t="inlineStr">
         <is>
-          <t>采矿</t>
+          <t>炸弹</t>
         </is>
       </c>
       <c r="B35" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C35" s="3" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="D35" s="3" t="n">
         <v>0</v>
       </c>
       <c r="E35" s="3" t="n">
-        <v>2</v>
+        <v>89</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="3" t="inlineStr">
         <is>
-          <t>采矿</t>
+          <t>炸弹</t>
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="D36" s="3" t="n">
         <v>0</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>3</v>
+        <v>160</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="3" t="inlineStr">
         <is>
-          <t>采矿</t>
+          <t>寒冰</t>
         </is>
       </c>
       <c r="B37" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C37" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="D37" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E37" s="3" t="n">
         <v>2</v>
-      </c>
-      <c r="C37" s="3" t="n">
-        <v>15</v>
-      </c>
-      <c r="D37" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E37" s="3" t="n">
-        <v>5</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="inlineStr">
         <is>
-          <t>采矿</t>
+          <t>寒冰</t>
         </is>
       </c>
       <c r="B38" s="3" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C38" s="3" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="D38" s="3" t="n">
         <v>0</v>
       </c>
       <c r="E38" s="3" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="3" t="inlineStr">
         <is>
-          <t>采矿</t>
+          <t>寒冰</t>
         </is>
       </c>
       <c r="B39" s="3" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C39" s="3" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="D39" s="3" t="n">
         <v>0</v>
       </c>
       <c r="E39" s="3" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="3" t="inlineStr">
         <is>
+          <t>寒冰</t>
+        </is>
+      </c>
+      <c r="B40" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C40" s="3" t="n">
+        <v>20</v>
+      </c>
+      <c r="D40" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E40" s="3" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="3" t="inlineStr">
+        <is>
+          <t>寒冰</t>
+        </is>
+      </c>
+      <c r="B41" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C41" s="3" t="n">
+        <v>25</v>
+      </c>
+      <c r="D41" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E41" s="3" t="n">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="3" t="inlineStr">
+        <is>
+          <t>寒冰</t>
+        </is>
+      </c>
+      <c r="B42" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="C42" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="D42" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E42" s="3" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="3" t="inlineStr">
+        <is>
+          <t>寒冰</t>
+        </is>
+      </c>
+      <c r="B43" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="C43" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="D43" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E43" s="3" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="3" t="inlineStr">
+        <is>
+          <t>寒冰</t>
+        </is>
+      </c>
+      <c r="B44" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="C44" s="3" t="n">
+        <v>15</v>
+      </c>
+      <c r="D44" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E44" s="3" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="3" t="inlineStr">
+        <is>
+          <t>寒冰</t>
+        </is>
+      </c>
+      <c r="B45" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="C45" s="3" t="n">
+        <v>20</v>
+      </c>
+      <c r="D45" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E45" s="3" t="n">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="3" t="inlineStr">
+        <is>
+          <t>寒冰</t>
+        </is>
+      </c>
+      <c r="B46" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="C46" s="3" t="n">
+        <v>25</v>
+      </c>
+      <c r="D46" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E46" s="3" t="n">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="3" t="inlineStr">
+        <is>
+          <t>寒冰</t>
+        </is>
+      </c>
+      <c r="B47" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="C47" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="D47" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E47" s="3" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="3" t="inlineStr">
+        <is>
+          <t>寒冰</t>
+        </is>
+      </c>
+      <c r="B48" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="C48" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="D48" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E48" s="3" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="3" t="inlineStr">
+        <is>
+          <t>寒冰</t>
+        </is>
+      </c>
+      <c r="B49" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="C49" s="3" t="n">
+        <v>15</v>
+      </c>
+      <c r="D49" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E49" s="3" t="n">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="3" t="inlineStr">
+        <is>
+          <t>寒冰</t>
+        </is>
+      </c>
+      <c r="B50" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="C50" s="3" t="n">
+        <v>20</v>
+      </c>
+      <c r="D50" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E50" s="3" t="n">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="3" t="inlineStr">
+        <is>
+          <t>寒冰</t>
+        </is>
+      </c>
+      <c r="B51" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="C51" s="3" t="n">
+        <v>25</v>
+      </c>
+      <c r="D51" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E51" s="3" t="n">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="3" t="inlineStr">
+        <is>
           <t>采矿</t>
         </is>
       </c>
-      <c r="B40" s="3" t="n">
+      <c r="B52" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C52" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="D52" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E52" s="3" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="3" t="inlineStr">
+        <is>
+          <t>采矿</t>
+        </is>
+      </c>
+      <c r="B53" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C53" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="D53" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E53" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="C40" s="3" t="n">
+    </row>
+    <row r="54">
+      <c r="A54" s="3" t="inlineStr">
+        <is>
+          <t>采矿</t>
+        </is>
+      </c>
+      <c r="B54" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C54" s="3" t="n">
         <v>15</v>
       </c>
-      <c r="D40" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E40" s="3" t="n">
-        <v>6</v>
+      <c r="D54" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E54" s="3" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="3" t="inlineStr">
+        <is>
+          <t>采矿</t>
+        </is>
+      </c>
+      <c r="B55" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C55" s="3" t="n">
+        <v>20</v>
+      </c>
+      <c r="D55" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E55" s="3" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="3" t="inlineStr">
+        <is>
+          <t>采矿</t>
+        </is>
+      </c>
+      <c r="B56" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C56" s="3" t="n">
+        <v>25</v>
+      </c>
+      <c r="D56" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E56" s="3" t="n">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="3" t="inlineStr">
+        <is>
+          <t>采矿</t>
+        </is>
+      </c>
+      <c r="B57" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="C57" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="D57" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E57" s="3" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="3" t="inlineStr">
+        <is>
+          <t>采矿</t>
+        </is>
+      </c>
+      <c r="B58" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="C58" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="D58" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E58" s="3" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="3" t="inlineStr">
+        <is>
+          <t>采矿</t>
+        </is>
+      </c>
+      <c r="B59" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="C59" s="3" t="n">
+        <v>15</v>
+      </c>
+      <c r="D59" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E59" s="3" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="3" t="inlineStr">
+        <is>
+          <t>采矿</t>
+        </is>
+      </c>
+      <c r="B60" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="C60" s="3" t="n">
+        <v>20</v>
+      </c>
+      <c r="D60" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E60" s="3" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="3" t="inlineStr">
+        <is>
+          <t>采矿</t>
+        </is>
+      </c>
+      <c r="B61" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="C61" s="3" t="n">
+        <v>25</v>
+      </c>
+      <c r="D61" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E61" s="3" t="n">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="3" t="inlineStr">
+        <is>
+          <t>采矿</t>
+        </is>
+      </c>
+      <c r="B62" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="C62" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="D62" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E62" s="3" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="3" t="inlineStr">
+        <is>
+          <t>采矿</t>
+        </is>
+      </c>
+      <c r="B63" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="C63" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="D63" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E63" s="3" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="3" t="inlineStr">
+        <is>
+          <t>采矿</t>
+        </is>
+      </c>
+      <c r="B64" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="C64" s="3" t="n">
+        <v>15</v>
+      </c>
+      <c r="D64" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E64" s="3" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="3" t="inlineStr">
+        <is>
+          <t>采矿</t>
+        </is>
+      </c>
+      <c r="B65" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="C65" s="3" t="n">
+        <v>20</v>
+      </c>
+      <c r="D65" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E65" s="3" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="3" t="inlineStr">
+        <is>
+          <t>采矿</t>
+        </is>
+      </c>
+      <c r="B66" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="C66" s="3" t="n">
+        <v>25</v>
+      </c>
+      <c r="D66" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E66" s="3" t="n">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="3" t="inlineStr">
+        <is>
+          <t>黑洞</t>
+        </is>
+      </c>
+      <c r="B67" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C67" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="D67" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E67" s="3" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="3" t="inlineStr">
+        <is>
+          <t>黑洞</t>
+        </is>
+      </c>
+      <c r="B68" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C68" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="D68" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E68" s="3" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="3" t="inlineStr">
+        <is>
+          <t>黑洞</t>
+        </is>
+      </c>
+      <c r="B69" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C69" s="3" t="n">
+        <v>15</v>
+      </c>
+      <c r="D69" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E69" s="3" t="n">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="3" t="inlineStr">
+        <is>
+          <t>黑洞</t>
+        </is>
+      </c>
+      <c r="B70" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C70" s="3" t="n">
+        <v>20</v>
+      </c>
+      <c r="D70" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E70" s="3" t="n">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="3" t="inlineStr">
+        <is>
+          <t>黑洞</t>
+        </is>
+      </c>
+      <c r="B71" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C71" s="3" t="n">
+        <v>25</v>
+      </c>
+      <c r="D71" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E71" s="3" t="n">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="3" t="inlineStr">
+        <is>
+          <t>黑洞</t>
+        </is>
+      </c>
+      <c r="B72" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="C72" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="D72" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E72" s="3" t="n">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="3" t="inlineStr">
+        <is>
+          <t>黑洞</t>
+        </is>
+      </c>
+      <c r="B73" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="C73" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="D73" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E73" s="3" t="n">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="3" t="inlineStr">
+        <is>
+          <t>黑洞</t>
+        </is>
+      </c>
+      <c r="B74" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="C74" s="3" t="n">
+        <v>15</v>
+      </c>
+      <c r="D74" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E74" s="3" t="n">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="3" t="inlineStr">
+        <is>
+          <t>黑洞</t>
+        </is>
+      </c>
+      <c r="B75" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="C75" s="3" t="n">
+        <v>20</v>
+      </c>
+      <c r="D75" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E75" s="3" t="n">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="3" t="inlineStr">
+        <is>
+          <t>黑洞</t>
+        </is>
+      </c>
+      <c r="B76" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="C76" s="3" t="n">
+        <v>25</v>
+      </c>
+      <c r="D76" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E76" s="3" t="n">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="3" t="inlineStr">
+        <is>
+          <t>黑洞</t>
+        </is>
+      </c>
+      <c r="B77" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="C77" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="D77" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E77" s="3" t="n">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="3" t="inlineStr">
+        <is>
+          <t>黑洞</t>
+        </is>
+      </c>
+      <c r="B78" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="C78" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="D78" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E78" s="3" t="n">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="3" t="inlineStr">
+        <is>
+          <t>黑洞</t>
+        </is>
+      </c>
+      <c r="B79" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="C79" s="3" t="n">
+        <v>15</v>
+      </c>
+      <c r="D79" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E79" s="3" t="n">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="3" t="inlineStr">
+        <is>
+          <t>黑洞</t>
+        </is>
+      </c>
+      <c r="B80" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="C80" s="3" t="n">
+        <v>20</v>
+      </c>
+      <c r="D80" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E80" s="3" t="n">
+        <v>532</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="3" t="inlineStr">
+        <is>
+          <t>黑洞</t>
+        </is>
+      </c>
+      <c r="B81" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="C81" s="3" t="n">
+        <v>25</v>
+      </c>
+      <c r="D81" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E81" s="3" t="n">
+        <v>958</v>
       </c>
     </row>
   </sheetData>
@@ -4840,19 +6828,19 @@
         <v>1</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E2" s="3" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="F2" s="3" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="G2" s="3" t="n">
         <v>5</v>
       </c>
       <c r="H2" s="3" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="I2" s="3" t="inlineStr">
         <is>
@@ -4871,19 +6859,19 @@
         <v>1</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="E3" s="3" t="n">
-        <v>0.09089999999999999</v>
+        <v>0.1818</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>11</v>
+        <v>5.5</v>
       </c>
       <c r="G3" s="3" t="n">
         <v>9</v>
       </c>
       <c r="H3" s="3" t="n">
-        <v>99</v>
+        <v>49.5</v>
       </c>
       <c r="I3" s="3" t="inlineStr">
         <is>
@@ -4902,19 +6890,19 @@
         <v>1</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="E4" s="3" t="n">
-        <v>0.0833</v>
+        <v>0.1667</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="G4" s="3" t="n">
         <v>16</v>
       </c>
       <c r="H4" s="3" t="n">
-        <v>192</v>
+        <v>96</v>
       </c>
       <c r="I4" s="3" t="inlineStr">
         <is>
@@ -4933,19 +6921,19 @@
         <v>1</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="E5" s="3" t="n">
-        <v>0.0769</v>
+        <v>0.1538</v>
       </c>
       <c r="F5" s="3" t="n">
-        <v>13</v>
+        <v>6.5</v>
       </c>
       <c r="G5" s="3" t="n">
         <v>29</v>
       </c>
       <c r="H5" s="3" t="n">
-        <v>377</v>
+        <v>188.5</v>
       </c>
       <c r="I5" s="3" t="inlineStr">
         <is>
@@ -4964,19 +6952,19 @@
         <v>1</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="E6" s="3" t="n">
-        <v>0.07140000000000001</v>
+        <v>0.1429</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="G6" s="3" t="n">
         <v>52</v>
       </c>
       <c r="H6" s="3" t="n">
-        <v>728</v>
+        <v>364</v>
       </c>
       <c r="I6" s="3" t="inlineStr">
         <is>
@@ -5294,10 +7282,10 @@
         <v>2</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E2" s="3" t="n">
-        <v>0.12</v>
+        <v>0.2</v>
       </c>
       <c r="F2" s="3" t="n">
         <v>0.3</v>
@@ -5325,16 +7313,16 @@
         <v>2</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E3" s="3" t="n">
-        <v>0.1111</v>
+        <v>0.1818</v>
       </c>
       <c r="F3" s="3" t="n">
         <v>0.3</v>
       </c>
       <c r="G3" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H3" s="3" t="n">
         <v>2.5</v>
@@ -5356,16 +7344,16 @@
         <v>2</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E4" s="3" t="n">
-        <v>0.1034</v>
+        <v>0.1667</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H4" s="3" t="n">
         <v>2.5</v>
@@ -5390,13 +7378,13 @@
         <v>11</v>
       </c>
       <c r="E5" s="3" t="n">
-        <v>0.0968</v>
+        <v>0.1538</v>
       </c>
       <c r="F5" s="3" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="G5" s="3" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H5" s="3" t="n">
         <v>2.5</v>
@@ -5418,16 +7406,16 @@
         <v>2</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E6" s="3" t="n">
-        <v>0.09089999999999999</v>
+        <v>0.1429</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="H6" s="3" t="n">
         <v>2.5</v>
@@ -5537,16 +7525,16 @@
         <v>2</v>
       </c>
       <c r="B3" s="3" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C3" s="3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D3" s="3" t="n">
         <v>3</v>
       </c>
       <c r="E3" s="3" t="n">
-        <v>0.333</v>
+        <v>1</v>
       </c>
       <c r="F3" s="3" t="n">
         <v>3</v>
@@ -5565,16 +7553,16 @@
         <v>3</v>
       </c>
       <c r="B4" s="3" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="D4" s="3" t="n">
         <v>3</v>
       </c>
       <c r="E4" s="3" t="n">
-        <v>0.333</v>
+        <v>2.667</v>
       </c>
       <c r="F4" s="3" t="n">
         <v>3</v>
@@ -5782,13 +7770,13 @@
         <v>7</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E4" s="3" t="n">
         <v>32</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>4.75</v>
+        <v>2.85</v>
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
@@ -5807,13 +7795,13 @@
         <v>8.5</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="E5" s="3" t="n">
         <v>50</v>
       </c>
       <c r="F5" s="3" t="n">
-        <v>12.5</v>
+        <v>5</v>
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
@@ -5891,11 +7879,11 @@
         </is>
       </c>
       <c r="B13" s="3" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>5.00</t>
+          <t>2.00</t>
         </is>
       </c>
     </row>
@@ -5906,11 +7894,11 @@
         </is>
       </c>
       <c r="B14" s="3" t="n">
-        <v>12.5</v>
+        <v>5</v>
       </c>
       <c r="C14" s="3" t="inlineStr">
         <is>
-          <t>12.50</t>
+          <t>5.00</t>
         </is>
       </c>
     </row>

--- a/docs/数值分析_模块怪物波次.xlsx
+++ b/docs/数值分析_模块怪物波次.xlsx
@@ -9,7 +9,7 @@
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="00_说明" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="01_全局" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="02_模块" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="02_模块总表" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="03_熔炉" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="04_波次" sheetId="5" state="visible" r:id="rId5"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="05_商店价" sheetId="6" state="visible" r:id="rId6"/>
@@ -449,7 +449,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B17"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -471,7 +471,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>docs/数值平衡表.md</t>
+          <t>docs/数值平衡表.md / docs/游戏策划案.md</t>
         </is>
       </c>
     </row>
@@ -493,67 +493,67 @@
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>约定</t>
+          <t>工作表</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>能量</t>
+          <t>01_全局</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>有效输出 ≈ 熔炉吞吐 × 环路投能次数 × 伤/能</t>
+          <t>开局与常量</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>生存</t>
+          <t>02_模块总表</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>沙漏毫秒；普通击杀不补沙</t>
+          <t>★各模块每级数值/小描述/描述/满能DPS（方便手改）</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>刷怪</t>
+          <t>03_熔炉</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>固定红/黄/蓝配额，仅打乱顺序</t>
+          <t>四维档位</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>HP</t>
+          <t>04_波次</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>黄=⌈红×0.5⌉；蓝=红×4；红每5波换档</t>
+          <t>26 波配额/HP/间隔/金币预算（波26=Boss）</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>商店</t>
+          <t>05_商店价</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>stage=(wave-1)//5；货架暂只出 Lv1</t>
+          <t>各模块等级标价</t>
         </is>
       </c>
     </row>
@@ -563,67 +563,55 @@
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>工作表</t>
+          <t>近期对齐</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>01_全局</t>
+          <t>总波数</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>开局与常量</t>
+          <t>26；波26仅 Boss HP=10000；Boss漏家即败</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>02_模块</t>
+          <t>补沙</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>等级要点（激光/炸弹/雪花/火花/矿机）</t>
+          <t>仅沙buff击杀；清波不补沙</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>03_熔炉</t>
+          <t>射速</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>四维档位</t>
+          <t>统一开火间隔概念；无独立冷却附魔</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>04_波次</t>
+          <t>奥数飞弹</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>25 波配额/HP/间隔/金币预算</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="1" t="inlineStr">
-        <is>
-          <t>05_商店价</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>各模块在关键波的 Lv1 标价</t>
+          <t>稀有；能耗1/容5/射速5；伤10/20/30/50/80；最右索敌</t>
         </is>
       </c>
     </row>
@@ -638,12 +626,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C12"/>
+  <dimension ref="A1:C17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="8" customWidth="1" min="1" max="1"/>
-    <col width="19" customWidth="1" min="2" max="2"/>
-    <col width="19" customWidth="1" min="3" max="3"/>
+    <col width="9" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="25" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -681,142 +669,231 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>25</v>
-      </c>
-      <c r="C3" s="3" t="inlineStr"/>
+        <v>26</v>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>1–25常规 + 26 Boss</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>开局沙 ms</t>
+          <t>Boss HP</t>
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>100000</v>
+        <v>10000</v>
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>沙尽即败</t>
+          <t>波26；漏家立刻败北</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>抽沙</t>
-        </is>
-      </c>
-      <c r="B5" s="3" t="inlineStr">
-        <is>
-          <t>1000 ms/秒</t>
-        </is>
+          <t>开局沙 ms</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="n">
+        <v>100000</v>
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>仅战斗</t>
+          <t>沙尽即败</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>手牌/商店</t>
+          <t>抽沙</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>8 / 6</t>
-        </is>
-      </c>
-      <c r="C6" s="3" t="inlineStr"/>
+          <t>1000 ms/秒</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>仅战斗</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>商店池上限</t>
-        </is>
-      </c>
-      <c r="B7" s="3" t="n">
-        <v>12</v>
+          <t>补沙</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>仅沙buff击杀</t>
+        </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>开局：激光+收束+雪花+火花</t>
+          <t>清波不补沙</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>球上限</t>
-        </is>
-      </c>
-      <c r="B8" s="3" t="n">
-        <v>40</v>
+          <t>手牌/商店</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>8 / 6</t>
+        </is>
       </c>
       <c r="C8" s="3" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>分解返还</t>
+          <t>商店池上限</t>
         </is>
       </c>
       <c r="B9" s="3" t="n">
-        <v>0.3</v>
+        <v>12</v>
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>invested×30%</t>
+          <t>开局：激光+收束+雪花+火花</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>扩展费用</t>
-        </is>
-      </c>
-      <c r="B10" s="3" t="inlineStr">
-        <is>
-          <t>100 / 300</t>
-        </is>
-      </c>
-      <c r="C10" s="3" t="inlineStr">
-        <is>
-          <t>3→5 / 5→7</t>
-        </is>
-      </c>
+          <t>球上限</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="n">
+        <v>40</v>
+      </c>
+      <c r="C10" s="3" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>刷新费</t>
+          <t>球寿命档</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>5+stage×(7+stage)</t>
+          <t>12/20/32/50 s</t>
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>同阶段恒定</t>
+          <t>熔炉寿命维</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>货架最高等级</t>
+          <t>分解返还</t>
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>1</v>
+        <v>0.3</v>
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t>ShopMaxOfferLevel</t>
+          <t>invested×30%</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>扩展费用</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>100 / 300</t>
+        </is>
+      </c>
+      <c r="C13" s="3" t="inlineStr">
+        <is>
+          <t>3→5 / 5→7</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="3" t="inlineStr">
+        <is>
+          <t>刷新费</t>
+        </is>
+      </c>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>5×((shopLv+1)/2)</t>
+        </is>
+      </c>
+      <c r="C14" s="3" t="inlineStr">
+        <is>
+          <t>商店 Lv1–2→5，Lv3–4→10…</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="3" t="inlineStr">
+        <is>
+          <t>商店等级</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>(wave-1)//5+1</t>
+        </is>
+      </c>
+      <c r="C15" s="3" t="inlineStr">
+        <is>
+          <t>每5波升1级；奇级单档/偶级双档</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="3" t="inlineStr">
+        <is>
+          <t>模块解锁</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>前15每3波，后每2波</t>
+        </is>
+      </c>
+      <c r="C16" s="3" t="inlineStr">
+        <is>
+          <t>3/6/9/12/16/18/20/22/24</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="3" t="inlineStr">
+        <is>
+          <t>熔炉/祝福</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>每5波至25</t>
+        </is>
+      </c>
+      <c r="C17" s="3" t="inlineStr">
+        <is>
+          <t>5/10/15/20/25</t>
         </is>
       </c>
     </row>
@@ -831,10 +908,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K8"/>
+  <dimension ref="A1:M77"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="42" customWidth="1" min="1" max="1"/>
+    <col width="48" customWidth="1" min="1" max="1"/>
     <col width="8" customWidth="1" min="2" max="2"/>
     <col width="8" customWidth="1" min="3" max="3"/>
     <col width="8" customWidth="1" min="4" max="4"/>
@@ -842,252 +919,3331 @@
     <col width="8" customWidth="1" min="6" max="6"/>
     <col width="8" customWidth="1" min="7" max="7"/>
     <col width="8" customWidth="1" min="8" max="8"/>
-    <col width="8" customWidth="1" min="9" max="9"/>
+    <col width="22" customWidth="1" min="9" max="9"/>
     <col width="8" customWidth="1" min="10" max="10"/>
     <col width="8" customWidth="1" min="11" max="11"/>
+    <col width="31" customWidth="1" min="12" max="12"/>
+    <col width="27" customWidth="1" min="13" max="13"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
+          <t>模块</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="inlineStr">
+        <is>
+          <t>稀有度</t>
+        </is>
+      </c>
+      <c r="C1" s="2" t="inlineStr">
+        <is>
           <t>Lv</t>
         </is>
       </c>
-      <c r="B1" s="2" t="inlineStr">
-        <is>
-          <t>激光伤</t>
-        </is>
-      </c>
-      <c r="C1" s="2" t="inlineStr">
-        <is>
-          <t>激光储能</t>
-        </is>
-      </c>
       <c r="D1" s="2" t="inlineStr">
         <is>
-          <t>激光间隔s</t>
+          <t>伤害</t>
         </is>
       </c>
       <c r="E1" s="2" t="inlineStr">
         <is>
-          <t>炸弹伤</t>
+          <t>能耗</t>
         </is>
       </c>
       <c r="F1" s="2" t="inlineStr">
         <is>
-          <t>炸弹半径</t>
+          <t>容量</t>
         </is>
       </c>
       <c r="G1" s="2" t="inlineStr">
         <is>
-          <t>雪花伤</t>
+          <t>射速发/秒</t>
         </is>
       </c>
       <c r="H1" s="2" t="inlineStr">
         <is>
-          <t>雪花寒时长s</t>
+          <t>间隔秒</t>
         </is>
       </c>
       <c r="I1" s="2" t="inlineStr">
         <is>
-          <t>火花伤</t>
+          <t>特殊效果</t>
         </is>
       </c>
       <c r="J1" s="2" t="inlineStr">
         <is>
-          <t>火花烧时长s</t>
+          <t>满能DPS</t>
         </is>
       </c>
       <c r="K1" s="2" t="inlineStr">
         <is>
-          <t>矿机金/次</t>
+          <t>小描述</t>
+        </is>
+      </c>
+      <c r="L1" s="2" t="inlineStr">
+        <is>
+          <t>描述</t>
+        </is>
+      </c>
+      <c r="M1" s="2" t="inlineStr">
+        <is>
+          <t>备注</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="3" t="n">
+      <c r="A2" s="3" t="inlineStr">
+        <is>
+          <t>激光</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="inlineStr">
+        <is>
+          <t>普通</t>
+        </is>
+      </c>
+      <c r="C2" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="B2" s="3" t="n">
-        <v>5</v>
-      </c>
-      <c r="C2" s="3" t="n">
-        <v>5</v>
-      </c>
       <c r="D2" s="3" t="n">
-        <v>0.2</v>
+        <v>5</v>
       </c>
       <c r="E2" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F2" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="G2" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="H2" s="3" t="inlineStr"/>
+      <c r="I2" s="3" t="inlineStr"/>
+      <c r="J2" s="3" t="n">
+        <v>25</v>
+      </c>
+      <c r="K2" s="3" t="inlineStr">
+        <is>
+          <t>单体激光</t>
+        </is>
+      </c>
+      <c r="L2" s="3" t="inlineStr">
+        <is>
+          <t>对最近敌人发射激光</t>
+        </is>
+      </c>
+      <c r="M2" s="3" t="inlineStr">
+        <is>
+          <t>查理激光塔</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>激光</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>普通</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="D3" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="E3" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F3" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="G3" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="H3" s="3" t="inlineStr"/>
+      <c r="I3" s="3" t="inlineStr"/>
+      <c r="J3" s="3" t="n">
+        <v>45</v>
+      </c>
+      <c r="K3" s="3" t="inlineStr">
+        <is>
+          <t>单体激光</t>
+        </is>
+      </c>
+      <c r="L3" s="3" t="inlineStr">
+        <is>
+          <t>对最近敌人发射激光</t>
+        </is>
+      </c>
+      <c r="M3" s="3" t="inlineStr">
+        <is>
+          <t>查理激光塔</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>激光</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>普通</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="D4" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="E4" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F4" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="G4" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="H4" s="3" t="inlineStr"/>
+      <c r="I4" s="3" t="inlineStr"/>
+      <c r="J4" s="3" t="n">
+        <v>80</v>
+      </c>
+      <c r="K4" s="3" t="inlineStr">
+        <is>
+          <t>单体激光</t>
+        </is>
+      </c>
+      <c r="L4" s="3" t="inlineStr">
+        <is>
+          <t>对最近敌人发射激光</t>
+        </is>
+      </c>
+      <c r="M4" s="3" t="inlineStr">
+        <is>
+          <t>查理激光塔</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>激光</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>普通</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="D5" s="3" t="n">
+        <v>29</v>
+      </c>
+      <c r="E5" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F5" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="G5" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="H5" s="3" t="inlineStr"/>
+      <c r="I5" s="3" t="inlineStr"/>
+      <c r="J5" s="3" t="n">
+        <v>145</v>
+      </c>
+      <c r="K5" s="3" t="inlineStr">
+        <is>
+          <t>单体激光</t>
+        </is>
+      </c>
+      <c r="L5" s="3" t="inlineStr">
+        <is>
+          <t>对最近敌人发射激光</t>
+        </is>
+      </c>
+      <c r="M5" s="3" t="inlineStr">
+        <is>
+          <t>查理激光塔</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>激光</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>普通</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="D6" s="3" t="n">
+        <v>52</v>
+      </c>
+      <c r="E6" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F6" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="G6" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="H6" s="3" t="inlineStr"/>
+      <c r="I6" s="3" t="inlineStr"/>
+      <c r="J6" s="3" t="n">
+        <v>260</v>
+      </c>
+      <c r="K6" s="3" t="inlineStr">
+        <is>
+          <t>单体激光</t>
+        </is>
+      </c>
+      <c r="L6" s="3" t="inlineStr">
+        <is>
+          <t>对最近敌人发射激光</t>
+        </is>
+      </c>
+      <c r="M6" s="3" t="inlineStr">
+        <is>
+          <t>查理激光塔</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>炸弹</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>普通</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D7" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="E7" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="F7" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="G7" s="3" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="H7" s="3" t="inlineStr"/>
+      <c r="I7" s="3" t="inlineStr">
+        <is>
+          <t>AOE半径1.5</t>
+        </is>
+      </c>
+      <c r="J7" s="3" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="K7" s="3" t="inlineStr">
+        <is>
+          <t>最左AOE</t>
+        </is>
+      </c>
+      <c r="L7" s="3" t="inlineStr">
+        <is>
+          <t>向最左敌人投掷炸弹爆炸</t>
+        </is>
+      </c>
+      <c r="M7" s="3" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="3" t="inlineStr">
+        <is>
+          <t>炸弹</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>普通</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="D8" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="E8" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="F8" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="G8" s="3" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="H8" s="3" t="inlineStr"/>
+      <c r="I8" s="3" t="inlineStr">
+        <is>
+          <t>AOE半径1.95</t>
+        </is>
+      </c>
+      <c r="J8" s="3" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="K8" s="3" t="inlineStr">
+        <is>
+          <t>最左AOE</t>
+        </is>
+      </c>
+      <c r="L8" s="3" t="inlineStr">
+        <is>
+          <t>向最左敌人投掷炸弹爆炸</t>
+        </is>
+      </c>
+      <c r="M8" s="3" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t>炸弹</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>普通</t>
+        </is>
+      </c>
+      <c r="C9" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="D9" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="E9" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="F9" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="G9" s="3" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="H9" s="3" t="inlineStr"/>
+      <c r="I9" s="3" t="inlineStr">
+        <is>
+          <t>AOE半径2.4</t>
+        </is>
+      </c>
+      <c r="J9" s="3" t="n">
+        <v>24</v>
+      </c>
+      <c r="K9" s="3" t="inlineStr">
+        <is>
+          <t>最左AOE</t>
+        </is>
+      </c>
+      <c r="L9" s="3" t="inlineStr">
+        <is>
+          <t>向最左敌人投掷炸弹爆炸</t>
+        </is>
+      </c>
+      <c r="M9" s="3" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="3" t="inlineStr">
+        <is>
+          <t>炸弹</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>普通</t>
+        </is>
+      </c>
+      <c r="C10" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="D10" s="3" t="n">
+        <v>29</v>
+      </c>
+      <c r="E10" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="F10" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="G10" s="3" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="H10" s="3" t="inlineStr"/>
+      <c r="I10" s="3" t="inlineStr">
+        <is>
+          <t>AOE半径2.85</t>
+        </is>
+      </c>
+      <c r="J10" s="3" t="n">
+        <v>43.5</v>
+      </c>
+      <c r="K10" s="3" t="inlineStr">
+        <is>
+          <t>最左AOE</t>
+        </is>
+      </c>
+      <c r="L10" s="3" t="inlineStr">
+        <is>
+          <t>向最左敌人投掷炸弹爆炸</t>
+        </is>
+      </c>
+      <c r="M10" s="3" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>炸弹</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>普通</t>
+        </is>
+      </c>
+      <c r="C11" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="D11" s="3" t="n">
+        <v>52</v>
+      </c>
+      <c r="E11" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="F11" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="G11" s="3" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="H11" s="3" t="inlineStr"/>
+      <c r="I11" s="3" t="inlineStr">
+        <is>
+          <t>AOE半径3.3</t>
+        </is>
+      </c>
+      <c r="J11" s="3" t="n">
+        <v>78</v>
+      </c>
+      <c r="K11" s="3" t="inlineStr">
+        <is>
+          <t>最左AOE</t>
+        </is>
+      </c>
+      <c r="L11" s="3" t="inlineStr">
+        <is>
+          <t>向最左敌人投掷炸弹爆炸</t>
+        </is>
+      </c>
+      <c r="M11" s="3" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="3" t="inlineStr">
+        <is>
+          <t>雪花</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>普通</t>
+        </is>
+      </c>
+      <c r="C12" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D12" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="E12" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F12" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="G12" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="H12" s="3" t="inlineStr"/>
+      <c r="I12" s="3" t="inlineStr">
+        <is>
+          <t>[寒冷]基础减速30% 2s</t>
+        </is>
+      </c>
+      <c r="J12" s="3" t="n">
+        <v>25</v>
+      </c>
+      <c r="K12" s="3" t="inlineStr">
+        <is>
+          <t>寒冷弹</t>
+        </is>
+      </c>
+      <c r="L12" s="3" t="inlineStr">
+        <is>
+          <t>向最左敌人发射雪花飞弹，可以使敌人获得[寒冷]</t>
+        </is>
+      </c>
+      <c r="M12" s="3" t="inlineStr">
+        <is>
+          <t>[寒冷]是状态；减速是其效果，可被寒冰增幅</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>雪花</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>普通</t>
+        </is>
+      </c>
+      <c r="C13" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="D13" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="E13" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F13" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="G13" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="H13" s="3" t="inlineStr"/>
+      <c r="I13" s="3" t="inlineStr">
+        <is>
+          <t>[寒冷]基础减速30% 3s</t>
+        </is>
+      </c>
+      <c r="J13" s="3" t="n">
+        <v>50</v>
+      </c>
+      <c r="K13" s="3" t="inlineStr">
+        <is>
+          <t>寒冷弹</t>
+        </is>
+      </c>
+      <c r="L13" s="3" t="inlineStr">
+        <is>
+          <t>向最左敌人发射雪花飞弹，可以使敌人获得[寒冷]</t>
+        </is>
+      </c>
+      <c r="M13" s="3" t="inlineStr">
+        <is>
+          <t>[寒冷]是状态；减速是其效果，可被寒冰增幅</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="3" t="inlineStr">
+        <is>
+          <t>雪花</t>
+        </is>
+      </c>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>普通</t>
+        </is>
+      </c>
+      <c r="C14" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="D14" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="E14" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F14" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="G14" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="H14" s="3" t="inlineStr"/>
+      <c r="I14" s="3" t="inlineStr">
+        <is>
+          <t>[寒冷]基础减速30% 4s</t>
+        </is>
+      </c>
+      <c r="J14" s="3" t="n">
+        <v>50</v>
+      </c>
+      <c r="K14" s="3" t="inlineStr">
+        <is>
+          <t>寒冷弹</t>
+        </is>
+      </c>
+      <c r="L14" s="3" t="inlineStr">
+        <is>
+          <t>向最左敌人发射雪花飞弹，可以使敌人获得[寒冷]</t>
+        </is>
+      </c>
+      <c r="M14" s="3" t="inlineStr">
+        <is>
+          <t>[寒冷]是状态；减速是其效果，可被寒冰增幅</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="3" t="inlineStr">
+        <is>
+          <t>雪花</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>普通</t>
+        </is>
+      </c>
+      <c r="C15" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="D15" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="E15" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F15" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="G15" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="H15" s="3" t="inlineStr"/>
+      <c r="I15" s="3" t="inlineStr">
+        <is>
+          <t>[寒冷]基础减速30% 5s</t>
+        </is>
+      </c>
+      <c r="J15" s="3" t="n">
+        <v>50</v>
+      </c>
+      <c r="K15" s="3" t="inlineStr">
+        <is>
+          <t>寒冷弹</t>
+        </is>
+      </c>
+      <c r="L15" s="3" t="inlineStr">
+        <is>
+          <t>向最左敌人发射雪花飞弹，可以使敌人获得[寒冷]</t>
+        </is>
+      </c>
+      <c r="M15" s="3" t="inlineStr">
+        <is>
+          <t>[寒冷]是状态；减速是其效果，可被寒冰增幅</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="3" t="inlineStr">
+        <is>
+          <t>雪花</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>普通</t>
+        </is>
+      </c>
+      <c r="C16" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="D16" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="E16" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F16" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="G16" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="H16" s="3" t="inlineStr"/>
+      <c r="I16" s="3" t="inlineStr">
+        <is>
+          <t>[寒冷]基础减速30% 6s</t>
+        </is>
+      </c>
+      <c r="J16" s="3" t="n">
+        <v>50</v>
+      </c>
+      <c r="K16" s="3" t="inlineStr">
+        <is>
+          <t>寒冷弹</t>
+        </is>
+      </c>
+      <c r="L16" s="3" t="inlineStr">
+        <is>
+          <t>向最左敌人发射雪花飞弹，可以使敌人获得[寒冷]</t>
+        </is>
+      </c>
+      <c r="M16" s="3" t="inlineStr">
+        <is>
+          <t>[寒冷]是状态；减速是其效果，可被寒冰增幅</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="3" t="inlineStr">
+        <is>
+          <t>火花</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>普通</t>
+        </is>
+      </c>
+      <c r="C17" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D17" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="E17" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F17" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="G17" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="H17" s="3" t="inlineStr"/>
+      <c r="I17" s="3" t="inlineStr">
+        <is>
+          <t>灼烧2.0s</t>
+        </is>
+      </c>
+      <c r="J17" s="3" t="n">
+        <v>25</v>
+      </c>
+      <c r="K17" s="3" t="inlineStr">
+        <is>
+          <t>灼烧弹</t>
+        </is>
+      </c>
+      <c r="L17" s="3" t="inlineStr">
+        <is>
+          <t>向最左敌人发射火花飞弹，可以使敌人获得[灼烧]</t>
+        </is>
+      </c>
+      <c r="M17" s="3" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="3" t="inlineStr">
+        <is>
+          <t>火花</t>
+        </is>
+      </c>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>普通</t>
+        </is>
+      </c>
+      <c r="C18" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="D18" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="E18" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F18" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="G18" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="H18" s="3" t="inlineStr"/>
+      <c r="I18" s="3" t="inlineStr">
+        <is>
+          <t>灼烧2.5s</t>
+        </is>
+      </c>
+      <c r="J18" s="3" t="n">
+        <v>50</v>
+      </c>
+      <c r="K18" s="3" t="inlineStr">
+        <is>
+          <t>灼烧弹</t>
+        </is>
+      </c>
+      <c r="L18" s="3" t="inlineStr">
+        <is>
+          <t>向最左敌人发射火花飞弹，可以使敌人获得[灼烧]</t>
+        </is>
+      </c>
+      <c r="M18" s="3" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="3" t="inlineStr">
+        <is>
+          <t>火花</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>普通</t>
+        </is>
+      </c>
+      <c r="C19" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="D19" s="3" t="n">
         <v>15</v>
       </c>
-      <c r="F2" s="3" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="G2" s="3" t="n">
-        <v>5</v>
-      </c>
-      <c r="H2" s="3" t="n">
+      <c r="E19" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F19" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="G19" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="H19" s="3" t="inlineStr"/>
+      <c r="I19" s="3" t="inlineStr">
+        <is>
+          <t>灼烧3.0s</t>
+        </is>
+      </c>
+      <c r="J19" s="3" t="n">
+        <v>75</v>
+      </c>
+      <c r="K19" s="3" t="inlineStr">
+        <is>
+          <t>灼烧弹</t>
+        </is>
+      </c>
+      <c r="L19" s="3" t="inlineStr">
+        <is>
+          <t>向最左敌人发射火花飞弹，可以使敌人获得[灼烧]</t>
+        </is>
+      </c>
+      <c r="M19" s="3" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="3" t="inlineStr">
+        <is>
+          <t>火花</t>
+        </is>
+      </c>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>普通</t>
+        </is>
+      </c>
+      <c r="C20" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="D20" s="3" t="n">
+        <v>20</v>
+      </c>
+      <c r="E20" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F20" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="G20" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="H20" s="3" t="inlineStr"/>
+      <c r="I20" s="3" t="inlineStr">
+        <is>
+          <t>灼烧3.5s</t>
+        </is>
+      </c>
+      <c r="J20" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="K20" s="3" t="inlineStr">
+        <is>
+          <t>灼烧弹</t>
+        </is>
+      </c>
+      <c r="L20" s="3" t="inlineStr">
+        <is>
+          <t>向最左敌人发射火花飞弹，可以使敌人获得[灼烧]</t>
+        </is>
+      </c>
+      <c r="M20" s="3" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="3" t="inlineStr">
+        <is>
+          <t>火花</t>
+        </is>
+      </c>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>普通</t>
+        </is>
+      </c>
+      <c r="C21" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="D21" s="3" t="n">
+        <v>30</v>
+      </c>
+      <c r="E21" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F21" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="G21" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="H21" s="3" t="inlineStr"/>
+      <c r="I21" s="3" t="inlineStr">
+        <is>
+          <t>灼烧4.0s</t>
+        </is>
+      </c>
+      <c r="J21" s="3" t="n">
+        <v>150</v>
+      </c>
+      <c r="K21" s="3" t="inlineStr">
+        <is>
+          <t>灼烧弹</t>
+        </is>
+      </c>
+      <c r="L21" s="3" t="inlineStr">
+        <is>
+          <t>向最左敌人发射火花飞弹，可以使敌人获得[灼烧]</t>
+        </is>
+      </c>
+      <c r="M21" s="3" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="3" t="inlineStr">
+        <is>
+          <t>激光炮</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>普通</t>
+        </is>
+      </c>
+      <c r="C22" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D22" s="3" t="n">
+        <v>30</v>
+      </c>
+      <c r="E22" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="F22" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="G22" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H22" s="3" t="inlineStr"/>
+      <c r="I22" s="3" t="inlineStr">
+        <is>
+          <t>厚激光</t>
+        </is>
+      </c>
+      <c r="J22" s="3" t="n">
+        <v>30</v>
+      </c>
+      <c r="K22" s="3" t="inlineStr">
+        <is>
+          <t>高伤激光</t>
+        </is>
+      </c>
+      <c r="L22" s="3" t="inlineStr">
+        <is>
+          <t>缓慢对最近敌人发射更大的激光</t>
+        </is>
+      </c>
+      <c r="M22" s="3" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="3" t="inlineStr">
+        <is>
+          <t>激光炮</t>
+        </is>
+      </c>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>普通</t>
+        </is>
+      </c>
+      <c r="C23" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="I2" s="3" t="n">
+      <c r="D23" s="3" t="n">
+        <v>60</v>
+      </c>
+      <c r="E23" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="F23" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="G23" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="J2" s="3" t="n">
+      <c r="H23" s="3" t="inlineStr"/>
+      <c r="I23" s="3" t="inlineStr">
+        <is>
+          <t>厚激光</t>
+        </is>
+      </c>
+      <c r="J23" s="3" t="n">
+        <v>60</v>
+      </c>
+      <c r="K23" s="3" t="inlineStr">
+        <is>
+          <t>高伤激光</t>
+        </is>
+      </c>
+      <c r="L23" s="3" t="inlineStr">
+        <is>
+          <t>缓慢对最近敌人发射更大的激光</t>
+        </is>
+      </c>
+      <c r="M23" s="3" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="3" t="inlineStr">
+        <is>
+          <t>激光炮</t>
+        </is>
+      </c>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>普通</t>
+        </is>
+      </c>
+      <c r="C24" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="D24" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="E24" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="F24" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="G24" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H24" s="3" t="inlineStr"/>
+      <c r="I24" s="3" t="inlineStr">
+        <is>
+          <t>厚激光</t>
+        </is>
+      </c>
+      <c r="J24" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="K24" s="3" t="inlineStr">
+        <is>
+          <t>高伤激光</t>
+        </is>
+      </c>
+      <c r="L24" s="3" t="inlineStr">
+        <is>
+          <t>缓慢对最近敌人发射更大的激光</t>
+        </is>
+      </c>
+      <c r="M24" s="3" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="3" t="inlineStr">
+        <is>
+          <t>激光炮</t>
+        </is>
+      </c>
+      <c r="B25" s="3" t="inlineStr">
+        <is>
+          <t>普通</t>
+        </is>
+      </c>
+      <c r="C25" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="D25" s="3" t="n">
+        <v>150</v>
+      </c>
+      <c r="E25" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="F25" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="G25" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H25" s="3" t="inlineStr"/>
+      <c r="I25" s="3" t="inlineStr">
+        <is>
+          <t>厚激光</t>
+        </is>
+      </c>
+      <c r="J25" s="3" t="n">
+        <v>150</v>
+      </c>
+      <c r="K25" s="3" t="inlineStr">
+        <is>
+          <t>高伤激光</t>
+        </is>
+      </c>
+      <c r="L25" s="3" t="inlineStr">
+        <is>
+          <t>缓慢对最近敌人发射更大的激光</t>
+        </is>
+      </c>
+      <c r="M25" s="3" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="3" t="inlineStr">
+        <is>
+          <t>激光炮</t>
+        </is>
+      </c>
+      <c r="B26" s="3" t="inlineStr">
+        <is>
+          <t>普通</t>
+        </is>
+      </c>
+      <c r="C26" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="D26" s="3" t="n">
+        <v>200</v>
+      </c>
+      <c r="E26" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="F26" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="G26" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H26" s="3" t="inlineStr"/>
+      <c r="I26" s="3" t="inlineStr">
+        <is>
+          <t>厚激光</t>
+        </is>
+      </c>
+      <c r="J26" s="3" t="n">
+        <v>200</v>
+      </c>
+      <c r="K26" s="3" t="inlineStr">
+        <is>
+          <t>高伤激光</t>
+        </is>
+      </c>
+      <c r="L26" s="3" t="inlineStr">
+        <is>
+          <t>缓慢对最近敌人发射更大的激光</t>
+        </is>
+      </c>
+      <c r="M26" s="3" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="3" t="inlineStr">
+        <is>
+          <t>奥数飞弹</t>
+        </is>
+      </c>
+      <c r="B27" s="3" t="inlineStr">
+        <is>
+          <t>稀有</t>
+        </is>
+      </c>
+      <c r="C27" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D27" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="E27" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F27" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="G27" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="H27" s="3" t="inlineStr"/>
+      <c r="I27" s="3" t="inlineStr">
+        <is>
+          <t>索敌最右</t>
+        </is>
+      </c>
+      <c r="J27" s="3" t="n">
+        <v>50</v>
+      </c>
+      <c r="K27" s="3" t="inlineStr">
+        <is>
+          <t>紫色飞弹</t>
+        </is>
+      </c>
+      <c r="L27" s="3" t="inlineStr">
+        <is>
+          <t>紫色索敌飞弹，锁定最右敌人</t>
+        </is>
+      </c>
+      <c r="M27" s="3" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="3" t="inlineStr">
+        <is>
+          <t>奥数飞弹</t>
+        </is>
+      </c>
+      <c r="B28" s="3" t="inlineStr">
+        <is>
+          <t>稀有</t>
+        </is>
+      </c>
+      <c r="C28" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="K2" s="3" t="n">
+      <c r="D28" s="3" t="n">
+        <v>20</v>
+      </c>
+      <c r="E28" s="3" t="n">
         <v>1</v>
       </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="3" t="n">
+      <c r="F28" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="G28" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="H28" s="3" t="inlineStr"/>
+      <c r="I28" s="3" t="inlineStr">
+        <is>
+          <t>索敌最右</t>
+        </is>
+      </c>
+      <c r="J28" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="K28" s="3" t="inlineStr">
+        <is>
+          <t>紫色飞弹</t>
+        </is>
+      </c>
+      <c r="L28" s="3" t="inlineStr">
+        <is>
+          <t>紫色索敌飞弹，锁定最右敌人</t>
+        </is>
+      </c>
+      <c r="M28" s="3" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="3" t="inlineStr">
+        <is>
+          <t>奥数飞弹</t>
+        </is>
+      </c>
+      <c r="B29" s="3" t="inlineStr">
+        <is>
+          <t>稀有</t>
+        </is>
+      </c>
+      <c r="C29" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="D29" s="3" t="n">
+        <v>30</v>
+      </c>
+      <c r="E29" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F29" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="G29" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="H29" s="3" t="inlineStr"/>
+      <c r="I29" s="3" t="inlineStr">
+        <is>
+          <t>索敌最右</t>
+        </is>
+      </c>
+      <c r="J29" s="3" t="n">
+        <v>150</v>
+      </c>
+      <c r="K29" s="3" t="inlineStr">
+        <is>
+          <t>紫色飞弹</t>
+        </is>
+      </c>
+      <c r="L29" s="3" t="inlineStr">
+        <is>
+          <t>紫色索敌飞弹，锁定最右敌人</t>
+        </is>
+      </c>
+      <c r="M29" s="3" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="3" t="inlineStr">
+        <is>
+          <t>奥数飞弹</t>
+        </is>
+      </c>
+      <c r="B30" s="3" t="inlineStr">
+        <is>
+          <t>稀有</t>
+        </is>
+      </c>
+      <c r="C30" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="D30" s="3" t="n">
+        <v>50</v>
+      </c>
+      <c r="E30" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F30" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="G30" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="H30" s="3" t="inlineStr"/>
+      <c r="I30" s="3" t="inlineStr">
+        <is>
+          <t>索敌最右</t>
+        </is>
+      </c>
+      <c r="J30" s="3" t="n">
+        <v>250</v>
+      </c>
+      <c r="K30" s="3" t="inlineStr">
+        <is>
+          <t>紫色飞弹</t>
+        </is>
+      </c>
+      <c r="L30" s="3" t="inlineStr">
+        <is>
+          <t>紫色索敌飞弹，锁定最右敌人</t>
+        </is>
+      </c>
+      <c r="M30" s="3" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="3" t="inlineStr">
+        <is>
+          <t>奥数飞弹</t>
+        </is>
+      </c>
+      <c r="B31" s="3" t="inlineStr">
+        <is>
+          <t>稀有</t>
+        </is>
+      </c>
+      <c r="C31" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="D31" s="3" t="n">
+        <v>80</v>
+      </c>
+      <c r="E31" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F31" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="G31" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="H31" s="3" t="inlineStr"/>
+      <c r="I31" s="3" t="inlineStr">
+        <is>
+          <t>索敌最右</t>
+        </is>
+      </c>
+      <c r="J31" s="3" t="n">
+        <v>400</v>
+      </c>
+      <c r="K31" s="3" t="inlineStr">
+        <is>
+          <t>紫色飞弹</t>
+        </is>
+      </c>
+      <c r="L31" s="3" t="inlineStr">
+        <is>
+          <t>紫色索敌飞弹，锁定最右敌人</t>
+        </is>
+      </c>
+      <c r="M31" s="3" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="3" t="inlineStr">
+        <is>
+          <t>热浪</t>
+        </is>
+      </c>
+      <c r="B32" s="3" t="inlineStr">
+        <is>
+          <t>稀有</t>
+        </is>
+      </c>
+      <c r="C32" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D32" s="3" t="inlineStr"/>
+      <c r="E32" s="3" t="n">
+        <v>20</v>
+      </c>
+      <c r="F32" s="3" t="n">
+        <v>20</v>
+      </c>
+      <c r="G32" s="3" t="inlineStr"/>
+      <c r="H32" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="I32" s="3" t="inlineStr">
+        <is>
+          <t>全屏灼烧2.0s</t>
+        </is>
+      </c>
+      <c r="J32" s="3" t="inlineStr"/>
+      <c r="K32" s="3" t="inlineStr">
+        <is>
+          <t>全屏灼烧</t>
+        </is>
+      </c>
+      <c r="L32" s="3" t="inlineStr">
+        <is>
+          <t>全屏敌人获得[灼烧]</t>
+        </is>
+      </c>
+      <c r="M32" s="3" t="inlineStr">
+        <is>
+          <t>射速以间隔秒显示</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="3" t="inlineStr">
+        <is>
+          <t>热浪</t>
+        </is>
+      </c>
+      <c r="B33" s="3" t="inlineStr">
+        <is>
+          <t>稀有</t>
+        </is>
+      </c>
+      <c r="C33" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="B3" s="3" t="n">
-        <v>9</v>
-      </c>
-      <c r="C3" s="3" t="n">
-        <v>7</v>
-      </c>
-      <c r="D3" s="3" t="n">
-        <v>0.182</v>
-      </c>
-      <c r="E3" s="3" t="n">
-        <v>22</v>
-      </c>
-      <c r="F3" s="3" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="G3" s="3" t="n">
-        <v>5</v>
-      </c>
-      <c r="H3" s="3" t="n">
+      <c r="D33" s="3" t="inlineStr"/>
+      <c r="E33" s="3" t="n">
+        <v>20</v>
+      </c>
+      <c r="F33" s="3" t="n">
+        <v>20</v>
+      </c>
+      <c r="G33" s="3" t="inlineStr"/>
+      <c r="H33" s="3" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="I33" s="3" t="inlineStr">
+        <is>
+          <t>全屏灼烧2.0s</t>
+        </is>
+      </c>
+      <c r="J33" s="3" t="inlineStr"/>
+      <c r="K33" s="3" t="inlineStr">
+        <is>
+          <t>全屏灼烧</t>
+        </is>
+      </c>
+      <c r="L33" s="3" t="inlineStr">
+        <is>
+          <t>全屏敌人获得[灼烧]</t>
+        </is>
+      </c>
+      <c r="M33" s="3" t="inlineStr">
+        <is>
+          <t>射速以间隔秒显示</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="3" t="inlineStr">
+        <is>
+          <t>热浪</t>
+        </is>
+      </c>
+      <c r="B34" s="3" t="inlineStr">
+        <is>
+          <t>稀有</t>
+        </is>
+      </c>
+      <c r="C34" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="I3" s="3" t="n">
+      <c r="D34" s="3" t="inlineStr"/>
+      <c r="E34" s="3" t="n">
+        <v>20</v>
+      </c>
+      <c r="F34" s="3" t="n">
+        <v>20</v>
+      </c>
+      <c r="G34" s="3" t="inlineStr"/>
+      <c r="H34" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="I34" s="3" t="inlineStr">
+        <is>
+          <t>全屏灼烧2.0s</t>
+        </is>
+      </c>
+      <c r="J34" s="3" t="inlineStr"/>
+      <c r="K34" s="3" t="inlineStr">
+        <is>
+          <t>全屏灼烧</t>
+        </is>
+      </c>
+      <c r="L34" s="3" t="inlineStr">
+        <is>
+          <t>全屏敌人获得[灼烧]</t>
+        </is>
+      </c>
+      <c r="M34" s="3" t="inlineStr">
+        <is>
+          <t>射速以间隔秒显示</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="3" t="inlineStr">
+        <is>
+          <t>热浪</t>
+        </is>
+      </c>
+      <c r="B35" s="3" t="inlineStr">
+        <is>
+          <t>稀有</t>
+        </is>
+      </c>
+      <c r="C35" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="D35" s="3" t="inlineStr"/>
+      <c r="E35" s="3" t="n">
+        <v>20</v>
+      </c>
+      <c r="F35" s="3" t="n">
+        <v>20</v>
+      </c>
+      <c r="G35" s="3" t="inlineStr"/>
+      <c r="H35" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="I35" s="3" t="inlineStr">
+        <is>
+          <t>全屏灼烧3.0s</t>
+        </is>
+      </c>
+      <c r="J35" s="3" t="inlineStr"/>
+      <c r="K35" s="3" t="inlineStr">
+        <is>
+          <t>全屏灼烧</t>
+        </is>
+      </c>
+      <c r="L35" s="3" t="inlineStr">
+        <is>
+          <t>全屏敌人获得[灼烧]</t>
+        </is>
+      </c>
+      <c r="M35" s="3" t="inlineStr">
+        <is>
+          <t>射速以间隔秒显示</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="3" t="inlineStr">
+        <is>
+          <t>热浪</t>
+        </is>
+      </c>
+      <c r="B36" s="3" t="inlineStr">
+        <is>
+          <t>稀有</t>
+        </is>
+      </c>
+      <c r="C36" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="D36" s="3" t="inlineStr"/>
+      <c r="E36" s="3" t="n">
+        <v>20</v>
+      </c>
+      <c r="F36" s="3" t="n">
+        <v>20</v>
+      </c>
+      <c r="G36" s="3" t="inlineStr"/>
+      <c r="H36" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="I36" s="3" t="inlineStr">
+        <is>
+          <t>全屏灼烧3.0s</t>
+        </is>
+      </c>
+      <c r="J36" s="3" t="inlineStr"/>
+      <c r="K36" s="3" t="inlineStr">
+        <is>
+          <t>全屏灼烧</t>
+        </is>
+      </c>
+      <c r="L36" s="3" t="inlineStr">
+        <is>
+          <t>全屏敌人获得[灼烧]</t>
+        </is>
+      </c>
+      <c r="M36" s="3" t="inlineStr">
+        <is>
+          <t>射速以间隔秒显示</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="3" t="inlineStr">
+        <is>
+          <t>冰霜冻结</t>
+        </is>
+      </c>
+      <c r="B37" s="3" t="inlineStr">
+        <is>
+          <t>稀有</t>
+        </is>
+      </c>
+      <c r="C37" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="J3" s="3" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="K3" s="3" t="n">
+      <c r="D37" s="3" t="inlineStr"/>
+      <c r="E37" s="3" t="n">
+        <v>20</v>
+      </c>
+      <c r="F37" s="3" t="n">
+        <v>20</v>
+      </c>
+      <c r="G37" s="3" t="inlineStr"/>
+      <c r="H37" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="I37" s="3" t="inlineStr">
+        <is>
+          <t>全屏[寒冷] 2.0s（基础减速30%）</t>
+        </is>
+      </c>
+      <c r="J37" s="3" t="inlineStr"/>
+      <c r="K37" s="3" t="inlineStr">
+        <is>
+          <t>全屏寒冷</t>
+        </is>
+      </c>
+      <c r="L37" s="3" t="inlineStr">
+        <is>
+          <t>全屏敌人获得[寒冷]</t>
+        </is>
+      </c>
+      <c r="M37" s="3" t="inlineStr">
+        <is>
+          <t>[寒冷]≠减速同义词；减速为基础效果，可被寒冰增幅</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="3" t="inlineStr">
+        <is>
+          <t>冰霜冻结</t>
+        </is>
+      </c>
+      <c r="B38" s="3" t="inlineStr">
+        <is>
+          <t>稀有</t>
+        </is>
+      </c>
+      <c r="C38" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="D38" s="3" t="inlineStr"/>
+      <c r="E38" s="3" t="n">
+        <v>20</v>
+      </c>
+      <c r="F38" s="3" t="n">
+        <v>20</v>
+      </c>
+      <c r="G38" s="3" t="inlineStr"/>
+      <c r="H38" s="3" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="I38" s="3" t="inlineStr">
+        <is>
+          <t>全屏[寒冷] 2.0s（基础减速30%）</t>
+        </is>
+      </c>
+      <c r="J38" s="3" t="inlineStr"/>
+      <c r="K38" s="3" t="inlineStr">
+        <is>
+          <t>全屏寒冷</t>
+        </is>
+      </c>
+      <c r="L38" s="3" t="inlineStr">
+        <is>
+          <t>全屏敌人获得[寒冷]</t>
+        </is>
+      </c>
+      <c r="M38" s="3" t="inlineStr">
+        <is>
+          <t>[寒冷]≠减速同义词；减速为基础效果，可被寒冰增幅</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="3" t="inlineStr">
+        <is>
+          <t>冰霜冻结</t>
+        </is>
+      </c>
+      <c r="B39" s="3" t="inlineStr">
+        <is>
+          <t>稀有</t>
+        </is>
+      </c>
+      <c r="C39" s="3" t="n">
         <v>3</v>
       </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="3" t="n">
+      <c r="D39" s="3" t="inlineStr"/>
+      <c r="E39" s="3" t="n">
+        <v>20</v>
+      </c>
+      <c r="F39" s="3" t="n">
+        <v>20</v>
+      </c>
+      <c r="G39" s="3" t="inlineStr"/>
+      <c r="H39" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="I39" s="3" t="inlineStr">
+        <is>
+          <t>全屏[寒冷] 2.0s（基础减速30%）</t>
+        </is>
+      </c>
+      <c r="J39" s="3" t="inlineStr"/>
+      <c r="K39" s="3" t="inlineStr">
+        <is>
+          <t>全屏寒冷</t>
+        </is>
+      </c>
+      <c r="L39" s="3" t="inlineStr">
+        <is>
+          <t>全屏敌人获得[寒冷]</t>
+        </is>
+      </c>
+      <c r="M39" s="3" t="inlineStr">
+        <is>
+          <t>[寒冷]≠减速同义词；减速为基础效果，可被寒冰增幅</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="3" t="inlineStr">
+        <is>
+          <t>冰霜冻结</t>
+        </is>
+      </c>
+      <c r="B40" s="3" t="inlineStr">
+        <is>
+          <t>稀有</t>
+        </is>
+      </c>
+      <c r="C40" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="D40" s="3" t="inlineStr"/>
+      <c r="E40" s="3" t="n">
+        <v>20</v>
+      </c>
+      <c r="F40" s="3" t="n">
+        <v>20</v>
+      </c>
+      <c r="G40" s="3" t="inlineStr"/>
+      <c r="H40" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="I40" s="3" t="inlineStr">
+        <is>
+          <t>全屏[寒冷] 3.0s（基础减速30%）</t>
+        </is>
+      </c>
+      <c r="J40" s="3" t="inlineStr"/>
+      <c r="K40" s="3" t="inlineStr">
+        <is>
+          <t>全屏寒冷</t>
+        </is>
+      </c>
+      <c r="L40" s="3" t="inlineStr">
+        <is>
+          <t>全屏敌人获得[寒冷]</t>
+        </is>
+      </c>
+      <c r="M40" s="3" t="inlineStr">
+        <is>
+          <t>[寒冷]≠减速同义词；减速为基础效果，可被寒冰增幅</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="3" t="inlineStr">
+        <is>
+          <t>冰霜冻结</t>
+        </is>
+      </c>
+      <c r="B41" s="3" t="inlineStr">
+        <is>
+          <t>稀有</t>
+        </is>
+      </c>
+      <c r="C41" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="D41" s="3" t="inlineStr"/>
+      <c r="E41" s="3" t="n">
+        <v>20</v>
+      </c>
+      <c r="F41" s="3" t="n">
+        <v>20</v>
+      </c>
+      <c r="G41" s="3" t="inlineStr"/>
+      <c r="H41" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="B4" s="3" t="n">
-        <v>16</v>
-      </c>
-      <c r="C4" s="3" t="n">
-        <v>9</v>
-      </c>
-      <c r="D4" s="3" t="n">
-        <v>0.167</v>
-      </c>
-      <c r="E4" s="3" t="n">
-        <v>34</v>
-      </c>
-      <c r="F4" s="3" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="G4" s="3" t="n">
-        <v>5</v>
-      </c>
-      <c r="H4" s="3" t="n">
+      <c r="I41" s="3" t="inlineStr">
+        <is>
+          <t>全屏[寒冷] 3.0s（基础减速30%）</t>
+        </is>
+      </c>
+      <c r="J41" s="3" t="inlineStr"/>
+      <c r="K41" s="3" t="inlineStr">
+        <is>
+          <t>全屏寒冷</t>
+        </is>
+      </c>
+      <c r="L41" s="3" t="inlineStr">
+        <is>
+          <t>全屏敌人获得[寒冷]</t>
+        </is>
+      </c>
+      <c r="M41" s="3" t="inlineStr">
+        <is>
+          <t>[寒冷]≠减速同义词；减速为基础效果，可被寒冰增幅</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="3" t="inlineStr">
+        <is>
+          <t>烈焰墙</t>
+        </is>
+      </c>
+      <c r="B42" s="3" t="inlineStr">
+        <is>
+          <t>稀有</t>
+        </is>
+      </c>
+      <c r="C42" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D42" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="E42" s="3" t="inlineStr"/>
+      <c r="F42" s="3" t="n">
+        <v>30</v>
+      </c>
+      <c r="G42" s="3" t="inlineStr"/>
+      <c r="H42" s="3" t="inlineStr"/>
+      <c r="I42" s="3" t="inlineStr">
+        <is>
+          <t>穿墙伤+灼烧2s</t>
+        </is>
+      </c>
+      <c r="J42" s="3" t="inlineStr"/>
+      <c r="K42" s="3" t="inlineStr">
+        <is>
+          <t>路径火墙</t>
+        </is>
+      </c>
+      <c r="L42" s="3" t="inlineStr">
+        <is>
+          <t>能量球穿过时造成伤害并挂烧</t>
+        </is>
+      </c>
+      <c r="M42" s="3" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="3" t="inlineStr">
+        <is>
+          <t>烈焰墙</t>
+        </is>
+      </c>
+      <c r="B43" s="3" t="inlineStr">
+        <is>
+          <t>稀有</t>
+        </is>
+      </c>
+      <c r="C43" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="D43" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="E43" s="3" t="inlineStr"/>
+      <c r="F43" s="3" t="n">
+        <v>30</v>
+      </c>
+      <c r="G43" s="3" t="inlineStr"/>
+      <c r="H43" s="3" t="inlineStr"/>
+      <c r="I43" s="3" t="inlineStr">
+        <is>
+          <t>穿墙伤+灼烧2s</t>
+        </is>
+      </c>
+      <c r="J43" s="3" t="inlineStr"/>
+      <c r="K43" s="3" t="inlineStr">
+        <is>
+          <t>路径火墙</t>
+        </is>
+      </c>
+      <c r="L43" s="3" t="inlineStr">
+        <is>
+          <t>能量球穿过时造成伤害并挂烧</t>
+        </is>
+      </c>
+      <c r="M43" s="3" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="3" t="inlineStr">
+        <is>
+          <t>烈焰墙</t>
+        </is>
+      </c>
+      <c r="B44" s="3" t="inlineStr">
+        <is>
+          <t>稀有</t>
+        </is>
+      </c>
+      <c r="C44" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="D44" s="3" t="n">
+        <v>15</v>
+      </c>
+      <c r="E44" s="3" t="inlineStr"/>
+      <c r="F44" s="3" t="n">
+        <v>30</v>
+      </c>
+      <c r="G44" s="3" t="inlineStr"/>
+      <c r="H44" s="3" t="inlineStr"/>
+      <c r="I44" s="3" t="inlineStr">
+        <is>
+          <t>穿墙伤+灼烧3s</t>
+        </is>
+      </c>
+      <c r="J44" s="3" t="inlineStr"/>
+      <c r="K44" s="3" t="inlineStr">
+        <is>
+          <t>路径火墙</t>
+        </is>
+      </c>
+      <c r="L44" s="3" t="inlineStr">
+        <is>
+          <t>能量球穿过时造成伤害并挂烧</t>
+        </is>
+      </c>
+      <c r="M44" s="3" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="3" t="inlineStr">
+        <is>
+          <t>烈焰墙</t>
+        </is>
+      </c>
+      <c r="B45" s="3" t="inlineStr">
+        <is>
+          <t>稀有</t>
+        </is>
+      </c>
+      <c r="C45" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="I4" s="3" t="n">
+      <c r="D45" s="3" t="n">
+        <v>29</v>
+      </c>
+      <c r="E45" s="3" t="inlineStr"/>
+      <c r="F45" s="3" t="n">
+        <v>30</v>
+      </c>
+      <c r="G45" s="3" t="inlineStr"/>
+      <c r="H45" s="3" t="inlineStr"/>
+      <c r="I45" s="3" t="inlineStr">
+        <is>
+          <t>穿墙伤+灼烧4s</t>
+        </is>
+      </c>
+      <c r="J45" s="3" t="inlineStr"/>
+      <c r="K45" s="3" t="inlineStr">
+        <is>
+          <t>路径火墙</t>
+        </is>
+      </c>
+      <c r="L45" s="3" t="inlineStr">
+        <is>
+          <t>能量球穿过时造成伤害并挂烧</t>
+        </is>
+      </c>
+      <c r="M45" s="3" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="3" t="inlineStr">
+        <is>
+          <t>烈焰墙</t>
+        </is>
+      </c>
+      <c r="B46" s="3" t="inlineStr">
+        <is>
+          <t>稀有</t>
+        </is>
+      </c>
+      <c r="C46" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="D46" s="3" t="n">
+        <v>50</v>
+      </c>
+      <c r="E46" s="3" t="inlineStr"/>
+      <c r="F46" s="3" t="n">
+        <v>30</v>
+      </c>
+      <c r="G46" s="3" t="inlineStr"/>
+      <c r="H46" s="3" t="inlineStr"/>
+      <c r="I46" s="3" t="inlineStr">
+        <is>
+          <t>穿墙伤+灼烧5s</t>
+        </is>
+      </c>
+      <c r="J46" s="3" t="inlineStr"/>
+      <c r="K46" s="3" t="inlineStr">
+        <is>
+          <t>路径火墙</t>
+        </is>
+      </c>
+      <c r="L46" s="3" t="inlineStr">
+        <is>
+          <t>能量球穿过时造成伤害并挂烧</t>
+        </is>
+      </c>
+      <c r="M46" s="3" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="3" t="inlineStr">
+        <is>
+          <t>火焰增幅</t>
+        </is>
+      </c>
+      <c r="B47" s="3" t="inlineStr">
+        <is>
+          <t>稀有</t>
+        </is>
+      </c>
+      <c r="C47" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D47" s="3" t="inlineStr"/>
+      <c r="E47" s="3" t="inlineStr"/>
+      <c r="F47" s="3" t="inlineStr"/>
+      <c r="G47" s="3" t="inlineStr"/>
+      <c r="H47" s="3" t="inlineStr"/>
+      <c r="I47" s="3" t="inlineStr">
+        <is>
+          <t>灼烧+1/0.5s</t>
+        </is>
+      </c>
+      <c r="J47" s="3" t="inlineStr"/>
+      <c r="K47" s="3" t="inlineStr">
+        <is>
+          <t>灼烧增幅</t>
+        </is>
+      </c>
+      <c r="L47" s="3" t="inlineStr">
+        <is>
+          <t>场上被动提高灼烧跳动伤害</t>
+        </is>
+      </c>
+      <c r="M47" s="3" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" s="3" t="inlineStr">
+        <is>
+          <t>火焰增幅</t>
+        </is>
+      </c>
+      <c r="B48" s="3" t="inlineStr">
+        <is>
+          <t>稀有</t>
+        </is>
+      </c>
+      <c r="C48" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="J4" s="3" t="n">
+      <c r="D48" s="3" t="inlineStr"/>
+      <c r="E48" s="3" t="inlineStr"/>
+      <c r="F48" s="3" t="inlineStr"/>
+      <c r="G48" s="3" t="inlineStr"/>
+      <c r="H48" s="3" t="inlineStr"/>
+      <c r="I48" s="3" t="inlineStr">
+        <is>
+          <t>灼烧+3/0.5s</t>
+        </is>
+      </c>
+      <c r="J48" s="3" t="inlineStr"/>
+      <c r="K48" s="3" t="inlineStr">
+        <is>
+          <t>灼烧增幅</t>
+        </is>
+      </c>
+      <c r="L48" s="3" t="inlineStr">
+        <is>
+          <t>场上被动提高灼烧跳动伤害</t>
+        </is>
+      </c>
+      <c r="M48" s="3" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" s="3" t="inlineStr">
+        <is>
+          <t>火焰增幅</t>
+        </is>
+      </c>
+      <c r="B49" s="3" t="inlineStr">
+        <is>
+          <t>稀有</t>
+        </is>
+      </c>
+      <c r="C49" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="K4" s="3" t="n">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="3" t="n">
+      <c r="D49" s="3" t="inlineStr"/>
+      <c r="E49" s="3" t="inlineStr"/>
+      <c r="F49" s="3" t="inlineStr"/>
+      <c r="G49" s="3" t="inlineStr"/>
+      <c r="H49" s="3" t="inlineStr"/>
+      <c r="I49" s="3" t="inlineStr">
+        <is>
+          <t>灼烧+5/0.5s</t>
+        </is>
+      </c>
+      <c r="J49" s="3" t="inlineStr"/>
+      <c r="K49" s="3" t="inlineStr">
+        <is>
+          <t>灼烧增幅</t>
+        </is>
+      </c>
+      <c r="L49" s="3" t="inlineStr">
+        <is>
+          <t>场上被动提高灼烧跳动伤害</t>
+        </is>
+      </c>
+      <c r="M49" s="3" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="3" t="inlineStr">
+        <is>
+          <t>火焰增幅</t>
+        </is>
+      </c>
+      <c r="B50" s="3" t="inlineStr">
+        <is>
+          <t>稀有</t>
+        </is>
+      </c>
+      <c r="C50" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="B5" s="3" t="n">
-        <v>29</v>
-      </c>
-      <c r="C5" s="3" t="n">
-        <v>11</v>
-      </c>
-      <c r="D5" s="3" t="n">
-        <v>0.154</v>
-      </c>
-      <c r="E5" s="3" t="n">
-        <v>51</v>
-      </c>
-      <c r="F5" s="3" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="G5" s="3" t="n">
-        <v>5</v>
-      </c>
-      <c r="H5" s="3" t="n">
-        <v>5</v>
-      </c>
-      <c r="I5" s="3" t="n">
+      <c r="D50" s="3" t="inlineStr"/>
+      <c r="E50" s="3" t="inlineStr"/>
+      <c r="F50" s="3" t="inlineStr"/>
+      <c r="G50" s="3" t="inlineStr"/>
+      <c r="H50" s="3" t="inlineStr"/>
+      <c r="I50" s="3" t="inlineStr">
+        <is>
+          <t>灼烧+7/0.5s</t>
+        </is>
+      </c>
+      <c r="J50" s="3" t="inlineStr"/>
+      <c r="K50" s="3" t="inlineStr">
+        <is>
+          <t>灼烧增幅</t>
+        </is>
+      </c>
+      <c r="L50" s="3" t="inlineStr">
+        <is>
+          <t>场上被动提高灼烧跳动伤害</t>
+        </is>
+      </c>
+      <c r="M50" s="3" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" s="3" t="inlineStr">
+        <is>
+          <t>火焰增幅</t>
+        </is>
+      </c>
+      <c r="B51" s="3" t="inlineStr">
+        <is>
+          <t>稀有</t>
+        </is>
+      </c>
+      <c r="C51" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="D51" s="3" t="inlineStr"/>
+      <c r="E51" s="3" t="inlineStr"/>
+      <c r="F51" s="3" t="inlineStr"/>
+      <c r="G51" s="3" t="inlineStr"/>
+      <c r="H51" s="3" t="inlineStr"/>
+      <c r="I51" s="3" t="inlineStr">
+        <is>
+          <t>灼烧+10/0.5s</t>
+        </is>
+      </c>
+      <c r="J51" s="3" t="inlineStr"/>
+      <c r="K51" s="3" t="inlineStr">
+        <is>
+          <t>灼烧增幅</t>
+        </is>
+      </c>
+      <c r="L51" s="3" t="inlineStr">
+        <is>
+          <t>场上被动提高灼烧跳动伤害</t>
+        </is>
+      </c>
+      <c r="M51" s="3" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" s="3" t="inlineStr">
+        <is>
+          <t>寒冰增幅</t>
+        </is>
+      </c>
+      <c r="B52" s="3" t="inlineStr">
+        <is>
+          <t>稀有</t>
+        </is>
+      </c>
+      <c r="C52" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D52" s="3" t="inlineStr"/>
+      <c r="E52" s="3" t="inlineStr"/>
+      <c r="F52" s="3" t="inlineStr"/>
+      <c r="G52" s="3" t="inlineStr"/>
+      <c r="H52" s="3" t="inlineStr"/>
+      <c r="I52" s="3" t="inlineStr">
+        <is>
+          <t>寒冷减速+5%（总上限70%）</t>
+        </is>
+      </c>
+      <c r="J52" s="3" t="inlineStr"/>
+      <c r="K52" s="3" t="inlineStr">
+        <is>
+          <t>寒冷增幅</t>
+        </is>
+      </c>
+      <c r="L52" s="3" t="inlineStr">
+        <is>
+          <t>场上被动：寒冷造成的减速每级+5%，总减速上限70%</t>
+        </is>
+      </c>
+      <c r="M52" s="3" t="inlineStr">
+        <is>
+          <t>[寒冷]状态的减速效果增幅</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="3" t="inlineStr">
+        <is>
+          <t>寒冰增幅</t>
+        </is>
+      </c>
+      <c r="B53" s="3" t="inlineStr">
+        <is>
+          <t>稀有</t>
+        </is>
+      </c>
+      <c r="C53" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="J5" s="3" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="K5" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="3" t="n">
-        <v>5</v>
-      </c>
-      <c r="B6" s="3" t="n">
-        <v>52</v>
-      </c>
-      <c r="C6" s="3" t="n">
-        <v>13</v>
-      </c>
-      <c r="D6" s="3" t="n">
-        <v>0.143</v>
-      </c>
-      <c r="E6" s="3" t="n">
-        <v>76</v>
-      </c>
-      <c r="F6" s="3" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="G6" s="3" t="n">
-        <v>5</v>
-      </c>
-      <c r="H6" s="3" t="n">
+      <c r="D53" s="3" t="inlineStr"/>
+      <c r="E53" s="3" t="inlineStr"/>
+      <c r="F53" s="3" t="inlineStr"/>
+      <c r="G53" s="3" t="inlineStr"/>
+      <c r="H53" s="3" t="inlineStr"/>
+      <c r="I53" s="3" t="inlineStr">
+        <is>
+          <t>寒冷减速+10%（总上限70%）</t>
+        </is>
+      </c>
+      <c r="J53" s="3" t="inlineStr"/>
+      <c r="K53" s="3" t="inlineStr">
+        <is>
+          <t>寒冷增幅</t>
+        </is>
+      </c>
+      <c r="L53" s="3" t="inlineStr">
+        <is>
+          <t>场上被动：寒冷造成的减速每级+5%，总减速上限70%</t>
+        </is>
+      </c>
+      <c r="M53" s="3" t="inlineStr">
+        <is>
+          <t>[寒冷]状态的减速效果增幅</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="3" t="inlineStr">
+        <is>
+          <t>寒冰增幅</t>
+        </is>
+      </c>
+      <c r="B54" s="3" t="inlineStr">
+        <is>
+          <t>稀有</t>
+        </is>
+      </c>
+      <c r="C54" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="D54" s="3" t="inlineStr"/>
+      <c r="E54" s="3" t="inlineStr"/>
+      <c r="F54" s="3" t="inlineStr"/>
+      <c r="G54" s="3" t="inlineStr"/>
+      <c r="H54" s="3" t="inlineStr"/>
+      <c r="I54" s="3" t="inlineStr">
+        <is>
+          <t>寒冷减速+15%（总上限70%）</t>
+        </is>
+      </c>
+      <c r="J54" s="3" t="inlineStr"/>
+      <c r="K54" s="3" t="inlineStr">
+        <is>
+          <t>寒冷增幅</t>
+        </is>
+      </c>
+      <c r="L54" s="3" t="inlineStr">
+        <is>
+          <t>场上被动：寒冷造成的减速每级+5%，总减速上限70%</t>
+        </is>
+      </c>
+      <c r="M54" s="3" t="inlineStr">
+        <is>
+          <t>[寒冷]状态的减速效果增幅</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="3" t="inlineStr">
+        <is>
+          <t>寒冰增幅</t>
+        </is>
+      </c>
+      <c r="B55" s="3" t="inlineStr">
+        <is>
+          <t>稀有</t>
+        </is>
+      </c>
+      <c r="C55" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="D55" s="3" t="inlineStr"/>
+      <c r="E55" s="3" t="inlineStr"/>
+      <c r="F55" s="3" t="inlineStr"/>
+      <c r="G55" s="3" t="inlineStr"/>
+      <c r="H55" s="3" t="inlineStr"/>
+      <c r="I55" s="3" t="inlineStr">
+        <is>
+          <t>寒冷减速+20%（总上限70%）</t>
+        </is>
+      </c>
+      <c r="J55" s="3" t="inlineStr"/>
+      <c r="K55" s="3" t="inlineStr">
+        <is>
+          <t>寒冷增幅</t>
+        </is>
+      </c>
+      <c r="L55" s="3" t="inlineStr">
+        <is>
+          <t>场上被动：寒冷造成的减速每级+5%，总减速上限70%</t>
+        </is>
+      </c>
+      <c r="M55" s="3" t="inlineStr">
+        <is>
+          <t>[寒冷]状态的减速效果增幅</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="3" t="inlineStr">
+        <is>
+          <t>寒冰增幅</t>
+        </is>
+      </c>
+      <c r="B56" s="3" t="inlineStr">
+        <is>
+          <t>稀有</t>
+        </is>
+      </c>
+      <c r="C56" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="D56" s="3" t="inlineStr"/>
+      <c r="E56" s="3" t="inlineStr"/>
+      <c r="F56" s="3" t="inlineStr"/>
+      <c r="G56" s="3" t="inlineStr"/>
+      <c r="H56" s="3" t="inlineStr"/>
+      <c r="I56" s="3" t="inlineStr">
+        <is>
+          <t>寒冷减速+25%（总上限70%）</t>
+        </is>
+      </c>
+      <c r="J56" s="3" t="inlineStr"/>
+      <c r="K56" s="3" t="inlineStr">
+        <is>
+          <t>寒冷增幅</t>
+        </is>
+      </c>
+      <c r="L56" s="3" t="inlineStr">
+        <is>
+          <t>场上被动：寒冷造成的减速每级+5%，总减速上限70%</t>
+        </is>
+      </c>
+      <c r="M56" s="3" t="inlineStr">
+        <is>
+          <t>[寒冷]状态的减速效果增幅</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="3" t="inlineStr">
+        <is>
+          <t>矿机</t>
+        </is>
+      </c>
+      <c r="B57" s="3" t="inlineStr">
+        <is>
+          <t>稀有</t>
+        </is>
+      </c>
+      <c r="C57" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D57" s="3" t="inlineStr"/>
+      <c r="E57" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="F57" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="G57" s="3" t="inlineStr"/>
+      <c r="H57" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="I57" s="3" t="inlineStr">
+        <is>
+          <t>5金/次</t>
+        </is>
+      </c>
+      <c r="J57" s="3" t="inlineStr"/>
+      <c r="K57" s="3" t="inlineStr">
+        <is>
+          <t>产金</t>
+        </is>
+      </c>
+      <c r="L57" s="3" t="inlineStr">
+        <is>
+          <t>耗能产金</t>
+        </is>
+      </c>
+      <c r="M57" s="3" t="inlineStr">
+        <is>
+          <t>最高Lv3</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="3" t="inlineStr">
+        <is>
+          <t>矿机</t>
+        </is>
+      </c>
+      <c r="B58" s="3" t="inlineStr">
+        <is>
+          <t>稀有</t>
+        </is>
+      </c>
+      <c r="C58" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="D58" s="3" t="inlineStr"/>
+      <c r="E58" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="F58" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="G58" s="3" t="inlineStr"/>
+      <c r="H58" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="I58" s="3" t="inlineStr">
+        <is>
+          <t>10金/次</t>
+        </is>
+      </c>
+      <c r="J58" s="3" t="inlineStr"/>
+      <c r="K58" s="3" t="inlineStr">
+        <is>
+          <t>产金</t>
+        </is>
+      </c>
+      <c r="L58" s="3" t="inlineStr">
+        <is>
+          <t>耗能产金</t>
+        </is>
+      </c>
+      <c r="M58" s="3" t="inlineStr">
+        <is>
+          <t>最高Lv3</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="3" t="inlineStr">
+        <is>
+          <t>矿机</t>
+        </is>
+      </c>
+      <c r="B59" s="3" t="inlineStr">
+        <is>
+          <t>稀有</t>
+        </is>
+      </c>
+      <c r="C59" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="D59" s="3" t="inlineStr"/>
+      <c r="E59" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="F59" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="G59" s="3" t="inlineStr"/>
+      <c r="H59" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="I59" s="3" t="inlineStr">
+        <is>
+          <t>20金/次</t>
+        </is>
+      </c>
+      <c r="J59" s="3" t="inlineStr"/>
+      <c r="K59" s="3" t="inlineStr">
+        <is>
+          <t>产金</t>
+        </is>
+      </c>
+      <c r="L59" s="3" t="inlineStr">
+        <is>
+          <t>耗能产金</t>
+        </is>
+      </c>
+      <c r="M59" s="3" t="inlineStr">
+        <is>
+          <t>最高Lv3</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="3" t="inlineStr">
+        <is>
+          <t>收束器</t>
+        </is>
+      </c>
+      <c r="B60" s="3" t="inlineStr">
+        <is>
+          <t>稀有</t>
+        </is>
+      </c>
+      <c r="C60" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D60" s="3" t="inlineStr"/>
+      <c r="E60" s="3" t="inlineStr"/>
+      <c r="F60" s="3" t="inlineStr"/>
+      <c r="G60" s="3" t="inlineStr"/>
+      <c r="H60" s="3" t="inlineStr"/>
+      <c r="I60" s="3" t="inlineStr"/>
+      <c r="J60" s="3" t="inlineStr"/>
+      <c r="K60" s="3" t="inlineStr">
+        <is>
+          <t>直角改向</t>
+        </is>
+      </c>
+      <c r="L60" s="3" t="inlineStr">
+        <is>
+          <t>将光球沿直角改向</t>
+        </is>
+      </c>
+      <c r="M60" s="3" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" s="3" t="inlineStr">
+        <is>
+          <t>传送门</t>
+        </is>
+      </c>
+      <c r="B61" s="3" t="inlineStr">
+        <is>
+          <t>稀有</t>
+        </is>
+      </c>
+      <c r="C61" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D61" s="3" t="inlineStr"/>
+      <c r="E61" s="3" t="inlineStr"/>
+      <c r="F61" s="3" t="inlineStr"/>
+      <c r="G61" s="3" t="inlineStr"/>
+      <c r="H61" s="3" t="inlineStr"/>
+      <c r="I61" s="3" t="inlineStr"/>
+      <c r="J61" s="3" t="inlineStr"/>
+      <c r="K61" s="3" t="inlineStr">
+        <is>
+          <t>成对传送</t>
+        </is>
+      </c>
+      <c r="L61" s="3" t="inlineStr">
+        <is>
+          <t>成对传送并保持方向，最多2座</t>
+        </is>
+      </c>
+      <c r="M61" s="3" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" s="3" t="inlineStr">
+        <is>
+          <t>中续器</t>
+        </is>
+      </c>
+      <c r="B62" s="3" t="inlineStr">
+        <is>
+          <t>稀有</t>
+        </is>
+      </c>
+      <c r="C62" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D62" s="3" t="inlineStr"/>
+      <c r="E62" s="3" t="inlineStr"/>
+      <c r="F62" s="3" t="inlineStr"/>
+      <c r="G62" s="3" t="inlineStr"/>
+      <c r="H62" s="3" t="inlineStr"/>
+      <c r="I62" s="3" t="inlineStr"/>
+      <c r="J62" s="3" t="inlineStr"/>
+      <c r="K62" s="3" t="inlineStr">
+        <is>
+          <t>汲能续寿</t>
+        </is>
+      </c>
+      <c r="L62" s="3" t="inlineStr">
+        <is>
+          <t>穿过汲能，满后刷新球寿命</t>
+        </is>
+      </c>
+      <c r="M62" s="3" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" s="3" t="inlineStr">
+        <is>
+          <t>加速器</t>
+        </is>
+      </c>
+      <c r="B63" s="3" t="inlineStr">
+        <is>
+          <t>稀有</t>
+        </is>
+      </c>
+      <c r="C63" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D63" s="3" t="inlineStr"/>
+      <c r="E63" s="3" t="inlineStr"/>
+      <c r="F63" s="3" t="inlineStr"/>
+      <c r="G63" s="3" t="inlineStr"/>
+      <c r="H63" s="3" t="inlineStr"/>
+      <c r="I63" s="3" t="inlineStr"/>
+      <c r="J63" s="3" t="inlineStr"/>
+      <c r="K63" s="3" t="inlineStr">
+        <is>
+          <t>球速×1.5</t>
+        </is>
+      </c>
+      <c r="L63" s="3" t="inlineStr">
+        <is>
+          <t>未加速球速度×1.5（每球一次）</t>
+        </is>
+      </c>
+      <c r="M63" s="3" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" s="3" t="inlineStr">
+        <is>
+          <t>火附魔</t>
+        </is>
+      </c>
+      <c r="B64" s="3" t="inlineStr">
+        <is>
+          <t>稀有</t>
+        </is>
+      </c>
+      <c r="C64" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D64" s="3" t="inlineStr"/>
+      <c r="E64" s="3" t="inlineStr"/>
+      <c r="F64" s="3" t="inlineStr"/>
+      <c r="G64" s="3" t="inlineStr"/>
+      <c r="H64" s="3" t="inlineStr"/>
+      <c r="I64" s="3" t="inlineStr"/>
+      <c r="J64" s="3" t="inlineStr"/>
+      <c r="K64" s="3" t="inlineStr">
+        <is>
+          <t>灼烧附魔格</t>
+        </is>
+      </c>
+      <c r="L64" s="3" t="inlineStr">
+        <is>
+          <t>种子格写入灼烧附魔</t>
+        </is>
+      </c>
+      <c r="M64" s="3" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" s="3" t="inlineStr">
+        <is>
+          <t>惊喜</t>
+        </is>
+      </c>
+      <c r="B65" s="3" t="inlineStr">
+        <is>
+          <t>稀有</t>
+        </is>
+      </c>
+      <c r="C65" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D65" s="3" t="inlineStr"/>
+      <c r="E65" s="3" t="inlineStr"/>
+      <c r="F65" s="3" t="inlineStr"/>
+      <c r="G65" s="3" t="inlineStr"/>
+      <c r="H65" s="3" t="inlineStr"/>
+      <c r="I65" s="3" t="inlineStr"/>
+      <c r="J65" s="3" t="inlineStr"/>
+      <c r="K65" s="3" t="inlineStr">
+        <is>
+          <t>随机附魔格</t>
+        </is>
+      </c>
+      <c r="L65" s="3" t="inlineStr">
+        <is>
+          <t>种子格写入随机附魔</t>
+        </is>
+      </c>
+      <c r="M65" s="3" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" s="3" t="inlineStr">
+        <is>
+          <t>火焰祝福</t>
+        </is>
+      </c>
+      <c r="B66" s="3" t="inlineStr">
+        <is>
+          <t>稀有</t>
+        </is>
+      </c>
+      <c r="C66" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D66" s="3" t="inlineStr"/>
+      <c r="E66" s="3" t="inlineStr"/>
+      <c r="F66" s="3" t="inlineStr"/>
+      <c r="G66" s="3" t="inlineStr"/>
+      <c r="H66" s="3" t="inlineStr"/>
+      <c r="I66" s="3" t="inlineStr"/>
+      <c r="J66" s="3" t="inlineStr"/>
+      <c r="K66" s="3" t="inlineStr">
+        <is>
+          <t>道具</t>
+        </is>
+      </c>
+      <c r="L66" s="3" t="inlineStr">
+        <is>
+          <t>手牌火焰祝福道具</t>
+        </is>
+      </c>
+      <c r="M66" s="3" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" s="3" t="inlineStr">
+        <is>
+          <t>净化</t>
+        </is>
+      </c>
+      <c r="B67" s="3" t="inlineStr">
+        <is>
+          <t>稀有</t>
+        </is>
+      </c>
+      <c r="C67" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D67" s="3" t="inlineStr"/>
+      <c r="E67" s="3" t="inlineStr"/>
+      <c r="F67" s="3" t="inlineStr"/>
+      <c r="G67" s="3" t="inlineStr"/>
+      <c r="H67" s="3" t="inlineStr"/>
+      <c r="I67" s="3" t="inlineStr"/>
+      <c r="J67" s="3" t="inlineStr"/>
+      <c r="K67" s="3" t="inlineStr">
+        <is>
+          <t>道具</t>
+        </is>
+      </c>
+      <c r="L67" s="3" t="inlineStr">
+        <is>
+          <t>净化诅咒/锁定</t>
+        </is>
+      </c>
+      <c r="M67" s="3" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" s="3" t="inlineStr">
+        <is>
+          <t>寒霜蘑菇</t>
+        </is>
+      </c>
+      <c r="B68" s="3" t="inlineStr">
+        <is>
+          <t>稀有</t>
+        </is>
+      </c>
+      <c r="C68" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D68" s="3" t="inlineStr"/>
+      <c r="E68" s="3" t="inlineStr"/>
+      <c r="F68" s="3" t="inlineStr"/>
+      <c r="G68" s="3" t="inlineStr"/>
+      <c r="H68" s="3" t="inlineStr"/>
+      <c r="I68" s="3" t="inlineStr"/>
+      <c r="J68" s="3" t="inlineStr"/>
+      <c r="K68" s="3" t="inlineStr">
+        <is>
+          <t>道具</t>
+        </is>
+      </c>
+      <c r="L68" s="3" t="inlineStr">
+        <is>
+          <t>紧急寒冷道具</t>
+        </is>
+      </c>
+      <c r="M68" s="3" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" s="3" t="inlineStr">
+        <is>
+          <t>黑洞</t>
+        </is>
+      </c>
+      <c r="B69" s="3" t="inlineStr">
+        <is>
+          <t>史诗</t>
+        </is>
+      </c>
+      <c r="C69" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D69" s="3" t="inlineStr"/>
+      <c r="E69" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="F69" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="G69" s="3" t="inlineStr"/>
+      <c r="H69" s="3" t="n">
         <v>6</v>
       </c>
-      <c r="I6" s="3" t="n">
+      <c r="I69" s="3" t="inlineStr">
+        <is>
+          <t>半径2.2 持续2.2s 吸力3.5</t>
+        </is>
+      </c>
+      <c r="J69" s="3" t="inlineStr"/>
+      <c r="K69" s="3" t="inlineStr">
+        <is>
+          <t>吸引聚怪</t>
+        </is>
+      </c>
+      <c r="L69" s="3" t="inlineStr">
+        <is>
+          <t>每6秒耗5能投掷黑洞吸引敌人（半径/时长/吸力随等级提升）</t>
+        </is>
+      </c>
+      <c r="M69" s="3" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" s="3" t="inlineStr">
+        <is>
+          <t>黑洞</t>
+        </is>
+      </c>
+      <c r="B70" s="3" t="inlineStr">
+        <is>
+          <t>史诗</t>
+        </is>
+      </c>
+      <c r="C70" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="D70" s="3" t="inlineStr"/>
+      <c r="E70" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="F70" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="G70" s="3" t="inlineStr"/>
+      <c r="H70" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="I70" s="3" t="inlineStr">
+        <is>
+          <t>半径2.75 持续2.6s 吸力4.3</t>
+        </is>
+      </c>
+      <c r="J70" s="3" t="inlineStr"/>
+      <c r="K70" s="3" t="inlineStr">
+        <is>
+          <t>吸引聚怪</t>
+        </is>
+      </c>
+      <c r="L70" s="3" t="inlineStr">
+        <is>
+          <t>每6秒耗5能投掷黑洞吸引敌人（半径/时长/吸力随等级提升）</t>
+        </is>
+      </c>
+      <c r="M70" s="3" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" s="3" t="inlineStr">
+        <is>
+          <t>黑洞</t>
+        </is>
+      </c>
+      <c r="B71" s="3" t="inlineStr">
+        <is>
+          <t>史诗</t>
+        </is>
+      </c>
+      <c r="C71" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="J6" s="3" t="n">
+      <c r="D71" s="3" t="inlineStr"/>
+      <c r="E71" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="F71" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="G71" s="3" t="inlineStr"/>
+      <c r="H71" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="I71" s="3" t="inlineStr">
+        <is>
+          <t>半径3.3 持续3.0s 吸力5.1</t>
+        </is>
+      </c>
+      <c r="J71" s="3" t="inlineStr"/>
+      <c r="K71" s="3" t="inlineStr">
+        <is>
+          <t>吸引聚怪</t>
+        </is>
+      </c>
+      <c r="L71" s="3" t="inlineStr">
+        <is>
+          <t>每6秒耗5能投掷黑洞吸引敌人（半径/时长/吸力随等级提升）</t>
+        </is>
+      </c>
+      <c r="M71" s="3" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" s="3" t="inlineStr">
+        <is>
+          <t>黑洞</t>
+        </is>
+      </c>
+      <c r="B72" s="3" t="inlineStr">
+        <is>
+          <t>史诗</t>
+        </is>
+      </c>
+      <c r="C72" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="K6" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="7"/>
-    <row r="8">
-      <c r="A8" s="4" t="inlineStr">
-        <is>
-          <t>雪花能耗1、寒30%；火花能耗1；炸弹能耗5；矿机能耗10、CD3s、最高Lv3。</t>
+      <c r="D72" s="3" t="inlineStr"/>
+      <c r="E72" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="F72" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="G72" s="3" t="inlineStr"/>
+      <c r="H72" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="I72" s="3" t="inlineStr">
+        <is>
+          <t>半径3.85 持续3.4s 吸力5.9</t>
+        </is>
+      </c>
+      <c r="J72" s="3" t="inlineStr"/>
+      <c r="K72" s="3" t="inlineStr">
+        <is>
+          <t>吸引聚怪</t>
+        </is>
+      </c>
+      <c r="L72" s="3" t="inlineStr">
+        <is>
+          <t>每6秒耗5能投掷黑洞吸引敌人（半径/时长/吸力随等级提升）</t>
+        </is>
+      </c>
+      <c r="M72" s="3" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="A73" s="3" t="inlineStr">
+        <is>
+          <t>黑洞</t>
+        </is>
+      </c>
+      <c r="B73" s="3" t="inlineStr">
+        <is>
+          <t>史诗</t>
+        </is>
+      </c>
+      <c r="C73" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="D73" s="3" t="inlineStr"/>
+      <c r="E73" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="F73" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="G73" s="3" t="inlineStr"/>
+      <c r="H73" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="I73" s="3" t="inlineStr">
+        <is>
+          <t>半径4.4 持续3.8s 吸力6.7</t>
+        </is>
+      </c>
+      <c r="J73" s="3" t="inlineStr"/>
+      <c r="K73" s="3" t="inlineStr">
+        <is>
+          <t>吸引聚怪</t>
+        </is>
+      </c>
+      <c r="L73" s="3" t="inlineStr">
+        <is>
+          <t>每6秒耗5能投掷黑洞吸引敌人（半径/时长/吸力随等级提升）</t>
+        </is>
+      </c>
+      <c r="M73" s="3" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="A74" s="3" t="inlineStr">
+        <is>
+          <t>聚变</t>
+        </is>
+      </c>
+      <c r="B74" s="3" t="inlineStr">
+        <is>
+          <t>史诗</t>
+        </is>
+      </c>
+      <c r="C74" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D74" s="3" t="inlineStr"/>
+      <c r="E74" s="3" t="inlineStr"/>
+      <c r="F74" s="3" t="inlineStr"/>
+      <c r="G74" s="3" t="inlineStr"/>
+      <c r="H74" s="3" t="inlineStr"/>
+      <c r="I74" s="3" t="inlineStr"/>
+      <c r="J74" s="3" t="inlineStr"/>
+      <c r="K74" s="3" t="inlineStr">
+        <is>
+          <t>五合一</t>
+        </is>
+      </c>
+      <c r="L74" s="3" t="inlineStr">
+        <is>
+          <t>5球合成1球</t>
+        </is>
+      </c>
+      <c r="M74" s="3" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" s="3" t="inlineStr">
+        <is>
+          <t>裂变</t>
+        </is>
+      </c>
+      <c r="B75" s="3" t="inlineStr">
+        <is>
+          <t>史诗</t>
+        </is>
+      </c>
+      <c r="C75" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D75" s="3" t="inlineStr"/>
+      <c r="E75" s="3" t="inlineStr"/>
+      <c r="F75" s="3" t="inlineStr"/>
+      <c r="G75" s="3" t="inlineStr"/>
+      <c r="H75" s="3" t="inlineStr"/>
+      <c r="I75" s="3" t="inlineStr"/>
+      <c r="J75" s="3" t="inlineStr"/>
+      <c r="K75" s="3" t="inlineStr">
+        <is>
+          <t>一变五</t>
+        </is>
+      </c>
+      <c r="L75" s="3" t="inlineStr">
+        <is>
+          <t>≥5能射出5颗默认球</t>
+        </is>
+      </c>
+      <c r="M75" s="3" t="inlineStr"/>
+    </row>
+    <row r="76">
+      <c r="A76" s="3" t="inlineStr">
+        <is>
+          <t>分裂器</t>
+        </is>
+      </c>
+      <c r="B76" s="3" t="inlineStr">
+        <is>
+          <t>史诗</t>
+        </is>
+      </c>
+      <c r="C76" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D76" s="3" t="inlineStr"/>
+      <c r="E76" s="3" t="inlineStr"/>
+      <c r="F76" s="3" t="inlineStr"/>
+      <c r="G76" s="3" t="inlineStr"/>
+      <c r="H76" s="3" t="inlineStr"/>
+      <c r="I76" s="3" t="inlineStr"/>
+      <c r="J76" s="3" t="inlineStr"/>
+      <c r="K76" s="3" t="inlineStr">
+        <is>
+          <t>一分二</t>
+        </is>
+      </c>
+      <c r="L76" s="3" t="inlineStr">
+        <is>
+          <t>T形分裂，寿命减半</t>
+        </is>
+      </c>
+      <c r="M76" s="3" t="inlineStr"/>
+    </row>
+    <row r="77">
+      <c r="A77" s="4" t="inlineStr">
+        <is>
+          <t>射速与间隔为同一概念（UI统称射速）。满能DPS≈伤×射速（可持续）。热浪/冰霜/矿机等控场经济类为空，请手改后同步 ModuleCatalog。</t>
         </is>
       </c>
     </row>
@@ -1188,13 +4344,13 @@
         <v>5.5</v>
       </c>
       <c r="E3" s="3" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="F3" s="3" t="n">
         <v>20</v>
       </c>
       <c r="G3" s="3" t="n">
-        <v>1.43</v>
+        <v>1.07</v>
       </c>
     </row>
     <row r="4">
@@ -1211,13 +4367,13 @@
         <v>7</v>
       </c>
       <c r="E4" s="3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F4" s="3" t="n">
         <v>32</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>2.86</v>
+        <v>1.9</v>
       </c>
     </row>
     <row r="5">
@@ -1234,13 +4390,13 @@
         <v>8.5</v>
       </c>
       <c r="E5" s="3" t="n">
-        <v>4</v>
+        <v>2.5</v>
       </c>
       <c r="F5" s="3" t="n">
         <v>50</v>
       </c>
       <c r="G5" s="3" t="n">
-        <v>5</v>
+        <v>3.12</v>
       </c>
     </row>
   </sheetData>
@@ -1254,7 +4410,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L26"/>
+  <dimension ref="A1:L27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -1264,7 +4420,7 @@
     <col width="8" customWidth="1" min="5" max="5"/>
     <col width="8" customWidth="1" min="6" max="6"/>
     <col width="8" customWidth="1" min="7" max="7"/>
-    <col width="8" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
     <col width="8" customWidth="1" min="9" max="9"/>
     <col width="8" customWidth="1" min="10" max="10"/>
     <col width="8" customWidth="1" min="11" max="11"/>
@@ -1527,28 +4683,28 @@
         <v>1</v>
       </c>
       <c r="C7" s="3" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="E7" s="3" t="n">
         <v>0</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>0.5</v>
+        <v>0.72</v>
       </c>
       <c r="H7" s="3" t="n">
         <v>25</v>
       </c>
       <c r="I7" s="3" t="n">
-        <v>506</v>
+        <v>291</v>
       </c>
       <c r="J7" s="3" t="n">
-        <v>4.06</v>
+        <v>1.91</v>
       </c>
       <c r="K7" s="3" t="n">
         <v>45</v>
@@ -1567,10 +4723,10 @@
         <v>1</v>
       </c>
       <c r="C8" s="3" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="D8" s="3" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="E8" s="3" t="n">
         <v>0</v>
@@ -1579,16 +4735,16 @@
         <v>2</v>
       </c>
       <c r="G8" s="3" t="n">
-        <v>0.42</v>
+        <v>0.55</v>
       </c>
       <c r="H8" s="3" t="n">
         <v>25</v>
       </c>
       <c r="I8" s="3" t="n">
-        <v>608</v>
+        <v>418</v>
       </c>
       <c r="J8" s="3" t="n">
-        <v>0.202</v>
+        <v>0.436</v>
       </c>
       <c r="K8" s="3" t="n">
         <v>55</v>
@@ -1603,28 +4759,28 @@
         <v>1</v>
       </c>
       <c r="C9" s="3" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="D9" s="3" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="E9" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F9" s="3" t="n">
         <v>2</v>
       </c>
       <c r="G9" s="3" t="n">
-        <v>0.34</v>
+        <v>0.42</v>
       </c>
       <c r="H9" s="3" t="n">
         <v>25</v>
       </c>
       <c r="I9" s="3" t="n">
-        <v>910</v>
+        <v>658</v>
       </c>
       <c r="J9" s="3" t="n">
-        <v>0.497</v>
+        <v>0.574</v>
       </c>
       <c r="K9" s="3" t="n">
         <v>65</v>
@@ -1639,28 +4795,28 @@
         <v>1</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F10" s="3" t="n">
         <v>2</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>0.26</v>
+        <v>0.3</v>
       </c>
       <c r="H10" s="3" t="n">
         <v>25</v>
       </c>
       <c r="I10" s="3" t="n">
-        <v>1138</v>
+        <v>949</v>
       </c>
       <c r="J10" s="3" t="n">
-        <v>0.251</v>
+        <v>0.442</v>
       </c>
       <c r="K10" s="3" t="n">
         <v>80</v>
@@ -1679,28 +4835,28 @@
         <v>1</v>
       </c>
       <c r="C11" s="3" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D11" s="3" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="E11" s="3" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F11" s="3" t="n">
         <v>2</v>
       </c>
       <c r="G11" s="3" t="n">
-        <v>0.16</v>
+        <v>0.18</v>
       </c>
       <c r="H11" s="3" t="n">
         <v>25</v>
       </c>
       <c r="I11" s="3" t="n">
-        <v>1568</v>
+        <v>1417</v>
       </c>
       <c r="J11" s="3" t="n">
-        <v>0.378</v>
+        <v>0.493</v>
       </c>
       <c r="K11" s="3" t="n">
         <v>95</v>
@@ -1734,13 +4890,13 @@
         <v>0.38</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="I12" s="3" t="n">
-        <v>3300</v>
+        <v>3960</v>
       </c>
       <c r="J12" s="3" t="n">
-        <v>1.105</v>
+        <v>1.795</v>
       </c>
       <c r="K12" s="3" t="n">
         <v>115</v>
@@ -1770,10 +4926,10 @@
         <v>0.3</v>
       </c>
       <c r="H13" s="3" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="I13" s="3" t="n">
-        <v>3700</v>
+        <v>4440</v>
       </c>
       <c r="J13" s="3" t="n">
         <v>0.121</v>
@@ -1810,10 +4966,10 @@
         <v>0.24</v>
       </c>
       <c r="H14" s="3" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="I14" s="3" t="n">
-        <v>4100</v>
+        <v>4920</v>
       </c>
       <c r="J14" s="3" t="n">
         <v>0.108</v>
@@ -1846,10 +5002,10 @@
         <v>0.18</v>
       </c>
       <c r="H15" s="3" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="I15" s="3" t="n">
-        <v>4500</v>
+        <v>5400</v>
       </c>
       <c r="J15" s="3" t="n">
         <v>0.098</v>
@@ -1882,10 +5038,10 @@
         <v>0.12</v>
       </c>
       <c r="H16" s="3" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="I16" s="3" t="n">
-        <v>5300</v>
+        <v>6360</v>
       </c>
       <c r="J16" s="3" t="n">
         <v>0.178</v>
@@ -1895,7 +5051,7 @@
       </c>
       <c r="L16" s="3" t="inlineStr">
         <is>
-          <t>模块+熔炉+祝福束缚</t>
+          <t>熔炉+祝福束缚</t>
         </is>
       </c>
     </row>
@@ -1922,18 +5078,22 @@
         <v>0.32</v>
       </c>
       <c r="H17" s="3" t="n">
-        <v>80</v>
+        <v>120</v>
       </c>
       <c r="I17" s="3" t="n">
-        <v>9440</v>
+        <v>14160</v>
       </c>
       <c r="J17" s="3" t="n">
-        <v>0.781</v>
+        <v>1.226</v>
       </c>
       <c r="K17" s="3" t="n">
         <v>295</v>
       </c>
-      <c r="L17" s="3" t="inlineStr"/>
+      <c r="L17" s="3" t="inlineStr">
+        <is>
+          <t>模块</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="3" t="n">
@@ -1958,10 +5118,10 @@
         <v>0.26</v>
       </c>
       <c r="H18" s="3" t="n">
-        <v>80</v>
+        <v>120</v>
       </c>
       <c r="I18" s="3" t="n">
-        <v>10400</v>
+        <v>15600</v>
       </c>
       <c r="J18" s="3" t="n">
         <v>0.102</v>
@@ -1994,10 +5154,10 @@
         <v>0.2</v>
       </c>
       <c r="H19" s="3" t="n">
-        <v>80</v>
+        <v>120</v>
       </c>
       <c r="I19" s="3" t="n">
-        <v>11680</v>
+        <v>17520</v>
       </c>
       <c r="J19" s="3" t="n">
         <v>0.123</v>
@@ -2034,10 +5194,10 @@
         <v>0.15</v>
       </c>
       <c r="H20" s="3" t="n">
-        <v>80</v>
+        <v>120</v>
       </c>
       <c r="I20" s="3" t="n">
-        <v>12960</v>
+        <v>19440</v>
       </c>
       <c r="J20" s="3" t="n">
         <v>0.11</v>
@@ -2070,10 +5230,10 @@
         <v>0.1</v>
       </c>
       <c r="H21" s="3" t="n">
-        <v>80</v>
+        <v>120</v>
       </c>
       <c r="I21" s="3" t="n">
-        <v>14560</v>
+        <v>21840</v>
       </c>
       <c r="J21" s="3" t="n">
         <v>0.123</v>
@@ -2083,7 +5243,7 @@
       </c>
       <c r="L21" s="3" t="inlineStr">
         <is>
-          <t>熔炉+祝福束缚</t>
+          <t>模块+熔炉+祝福束缚</t>
         </is>
       </c>
     </row>
@@ -2110,22 +5270,18 @@
         <v>0.28</v>
       </c>
       <c r="H22" s="3" t="n">
-        <v>130</v>
+        <v>200</v>
       </c>
       <c r="I22" s="3" t="n">
-        <v>25740</v>
+        <v>39600</v>
       </c>
       <c r="J22" s="3" t="n">
-        <v>0.768</v>
+        <v>0.8129999999999999</v>
       </c>
       <c r="K22" s="3" t="n">
         <v>750</v>
       </c>
-      <c r="L22" s="3" t="inlineStr">
-        <is>
-          <t>模块</t>
-        </is>
-      </c>
+      <c r="L22" s="3" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="3" t="n">
@@ -2150,10 +5306,10 @@
         <v>0.22</v>
       </c>
       <c r="H23" s="3" t="n">
-        <v>130</v>
+        <v>200</v>
       </c>
       <c r="I23" s="3" t="n">
-        <v>27820</v>
+        <v>42800</v>
       </c>
       <c r="J23" s="3" t="n">
         <v>0.081</v>
@@ -2161,7 +5317,11 @@
       <c r="K23" s="3" t="n">
         <v>905</v>
       </c>
-      <c r="L23" s="3" t="inlineStr"/>
+      <c r="L23" s="3" t="inlineStr">
+        <is>
+          <t>模块</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="3" t="n">
@@ -2186,10 +5346,10 @@
         <v>0.16</v>
       </c>
       <c r="H24" s="3" t="n">
-        <v>130</v>
+        <v>200</v>
       </c>
       <c r="I24" s="3" t="n">
-        <v>30290</v>
+        <v>46600</v>
       </c>
       <c r="J24" s="3" t="n">
         <v>0.089</v>
@@ -2222,10 +5382,10 @@
         <v>0.12</v>
       </c>
       <c r="H25" s="3" t="n">
-        <v>130</v>
+        <v>200</v>
       </c>
       <c r="I25" s="3" t="n">
-        <v>32760</v>
+        <v>50400</v>
       </c>
       <c r="J25" s="3" t="n">
         <v>0.082</v>
@@ -2262,10 +5422,10 @@
         <v>0.08</v>
       </c>
       <c r="H26" s="3" t="n">
-        <v>130</v>
+        <v>200</v>
       </c>
       <c r="I26" s="3" t="n">
-        <v>37440</v>
+        <v>57600</v>
       </c>
       <c r="J26" s="3" t="n">
         <v>0.143</v>
@@ -2273,7 +5433,47 @@
       <c r="K26" s="3" t="n">
         <v>1580</v>
       </c>
-      <c r="L26" s="3" t="inlineStr"/>
+      <c r="L26" s="3" t="inlineStr">
+        <is>
+          <t>熔炉+祝福束缚</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="3" t="n">
+        <v>26</v>
+      </c>
+      <c r="B27" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="C27" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D27" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E27" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F27" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G27" s="3" t="inlineStr"/>
+      <c r="H27" s="3" t="inlineStr">
+        <is>
+          <t>Boss 10000</t>
+        </is>
+      </c>
+      <c r="I27" s="3" t="n">
+        <v>10000</v>
+      </c>
+      <c r="J27" s="3" t="n">
+        <v>-0.826</v>
+      </c>
+      <c r="K27" s="3" t="n">
+        <v>1905</v>
+      </c>
+      <c r="L27" s="3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2286,7 +5486,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M18"/>
+  <dimension ref="A1:H26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -2295,13 +5495,8 @@
     <col width="8" customWidth="1" min="4" max="4"/>
     <col width="8" customWidth="1" min="5" max="5"/>
     <col width="8" customWidth="1" min="6" max="6"/>
-    <col width="9" customWidth="1" min="7" max="7"/>
-    <col width="9" customWidth="1" min="8" max="8"/>
-    <col width="9" customWidth="1" min="9" max="9"/>
-    <col width="9" customWidth="1" min="10" max="10"/>
-    <col width="9" customWidth="1" min="11" max="11"/>
-    <col width="9" customWidth="1" min="12" max="12"/>
-    <col width="9" customWidth="1" min="13" max="13"/>
+    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="8" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2322,52 +5517,27 @@
       </c>
       <c r="D1" s="2" t="inlineStr">
         <is>
-          <t>波1 Lv1</t>
+          <t>Lv1</t>
         </is>
       </c>
       <c r="E1" s="2" t="inlineStr">
         <is>
-          <t>波5 Lv1</t>
+          <t>Lv2</t>
         </is>
       </c>
       <c r="F1" s="2" t="inlineStr">
         <is>
-          <t>波6 Lv1</t>
+          <t>Lv3</t>
         </is>
       </c>
       <c r="G1" s="2" t="inlineStr">
         <is>
-          <t>波10 Lv1</t>
+          <t>Lv4</t>
         </is>
       </c>
       <c r="H1" s="2" t="inlineStr">
         <is>
-          <t>波11 Lv1</t>
-        </is>
-      </c>
-      <c r="I1" s="2" t="inlineStr">
-        <is>
-          <t>波15 Lv1</t>
-        </is>
-      </c>
-      <c r="J1" s="2" t="inlineStr">
-        <is>
-          <t>波16 Lv1</t>
-        </is>
-      </c>
-      <c r="K1" s="2" t="inlineStr">
-        <is>
-          <t>波20 Lv1</t>
-        </is>
-      </c>
-      <c r="L1" s="2" t="inlineStr">
-        <is>
-          <t>波21 Lv1</t>
-        </is>
-      </c>
-      <c r="M1" s="2" t="inlineStr">
-        <is>
-          <t>波25 Lv1</t>
+          <t>Lv5</t>
         </is>
       </c>
     </row>
@@ -2389,31 +5559,16 @@
         <v>10</v>
       </c>
       <c r="E2" s="3" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="F2" s="3" t="n">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="G2" s="3" t="n">
-        <v>20</v>
+        <v>115</v>
       </c>
       <c r="H2" s="3" t="n">
-        <v>30</v>
-      </c>
-      <c r="I2" s="3" t="n">
-        <v>30</v>
-      </c>
-      <c r="J2" s="3" t="n">
-        <v>60</v>
-      </c>
-      <c r="K2" s="3" t="n">
-        <v>60</v>
-      </c>
-      <c r="L2" s="3" t="n">
-        <v>105</v>
-      </c>
-      <c r="M2" s="3" t="n">
-        <v>105</v>
+        <v>255</v>
       </c>
     </row>
     <row r="3">
@@ -2434,31 +5589,16 @@
         <v>25</v>
       </c>
       <c r="E3" s="3" t="n">
-        <v>25</v>
+        <v>55</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>45</v>
+        <v>125</v>
       </c>
       <c r="G3" s="3" t="n">
-        <v>45</v>
+        <v>285</v>
       </c>
       <c r="H3" s="3" t="n">
-        <v>80</v>
-      </c>
-      <c r="I3" s="3" t="n">
-        <v>80</v>
-      </c>
-      <c r="J3" s="3" t="n">
-        <v>145</v>
-      </c>
-      <c r="K3" s="3" t="n">
-        <v>145</v>
-      </c>
-      <c r="L3" s="3" t="n">
-        <v>260</v>
-      </c>
-      <c r="M3" s="3" t="n">
-        <v>260</v>
+        <v>640</v>
       </c>
     </row>
     <row r="4">
@@ -2479,31 +5619,16 @@
         <v>15</v>
       </c>
       <c r="E4" s="3" t="n">
-        <v>15</v>
+        <v>35</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>25</v>
+        <v>75</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>25</v>
+        <v>170</v>
       </c>
       <c r="H4" s="3" t="n">
-        <v>50</v>
-      </c>
-      <c r="I4" s="3" t="n">
-        <v>50</v>
-      </c>
-      <c r="J4" s="3" t="n">
-        <v>85</v>
-      </c>
-      <c r="K4" s="3" t="n">
-        <v>85</v>
-      </c>
-      <c r="L4" s="3" t="n">
-        <v>155</v>
-      </c>
-      <c r="M4" s="3" t="n">
-        <v>155</v>
+        <v>385</v>
       </c>
     </row>
     <row r="5">
@@ -2524,31 +5649,16 @@
         <v>15</v>
       </c>
       <c r="E5" s="3" t="n">
-        <v>15</v>
+        <v>35</v>
       </c>
       <c r="F5" s="3" t="n">
-        <v>25</v>
+        <v>75</v>
       </c>
       <c r="G5" s="3" t="n">
-        <v>25</v>
+        <v>170</v>
       </c>
       <c r="H5" s="3" t="n">
-        <v>50</v>
-      </c>
-      <c r="I5" s="3" t="n">
-        <v>50</v>
-      </c>
-      <c r="J5" s="3" t="n">
-        <v>85</v>
-      </c>
-      <c r="K5" s="3" t="n">
-        <v>85</v>
-      </c>
-      <c r="L5" s="3" t="n">
-        <v>155</v>
-      </c>
-      <c r="M5" s="3" t="n">
-        <v>155</v>
+        <v>385</v>
       </c>
     </row>
     <row r="6">
@@ -2568,33 +5678,10 @@
       <c r="D6" s="3" t="n">
         <v>20</v>
       </c>
-      <c r="E6" s="3" t="n">
-        <v>20</v>
-      </c>
-      <c r="F6" s="3" t="n">
-        <v>40</v>
-      </c>
-      <c r="G6" s="3" t="n">
-        <v>40</v>
-      </c>
-      <c r="H6" s="3" t="n">
-        <v>75</v>
-      </c>
-      <c r="I6" s="3" t="n">
-        <v>75</v>
-      </c>
-      <c r="J6" s="3" t="n">
-        <v>130</v>
-      </c>
-      <c r="K6" s="3" t="n">
-        <v>130</v>
-      </c>
-      <c r="L6" s="3" t="n">
-        <v>235</v>
-      </c>
-      <c r="M6" s="3" t="n">
-        <v>235</v>
-      </c>
+      <c r="E6" s="3" t="inlineStr"/>
+      <c r="F6" s="3" t="inlineStr"/>
+      <c r="G6" s="3" t="inlineStr"/>
+      <c r="H6" s="3" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
@@ -2614,32 +5701,13 @@
         <v>25</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>50</v>
-      </c>
-      <c r="G7" s="3" t="n">
-        <v>50</v>
-      </c>
-      <c r="H7" s="3" t="n">
-        <v>85</v>
-      </c>
-      <c r="I7" s="3" t="n">
-        <v>85</v>
-      </c>
-      <c r="J7" s="3" t="n">
-        <v>155</v>
-      </c>
-      <c r="K7" s="3" t="n">
-        <v>155</v>
-      </c>
-      <c r="L7" s="3" t="n">
-        <v>285</v>
-      </c>
-      <c r="M7" s="3" t="n">
-        <v>285</v>
-      </c>
+        <v>45</v>
+      </c>
+      <c r="G7" s="3" t="inlineStr"/>
+      <c r="H7" s="3" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
@@ -2659,37 +5727,22 @@
         <v>30</v>
       </c>
       <c r="E8" s="3" t="n">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="F8" s="3" t="n">
         <v>55</v>
       </c>
       <c r="G8" s="3" t="n">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="H8" s="3" t="n">
-        <v>95</v>
-      </c>
-      <c r="I8" s="3" t="n">
-        <v>95</v>
-      </c>
-      <c r="J8" s="3" t="n">
-        <v>175</v>
-      </c>
-      <c r="K8" s="3" t="n">
-        <v>175</v>
-      </c>
-      <c r="L8" s="3" t="n">
-        <v>315</v>
-      </c>
-      <c r="M8" s="3" t="n">
-        <v>315</v>
+        <v>80</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>传送门</t>
+          <t>寒冰增幅</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
@@ -2698,43 +5751,28 @@
         </is>
       </c>
       <c r="C9" s="3" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D9" s="3" t="n">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="E9" s="3" t="n">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="F9" s="3" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="G9" s="3" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="H9" s="3" t="n">
-        <v>105</v>
-      </c>
-      <c r="I9" s="3" t="n">
-        <v>105</v>
-      </c>
-      <c r="J9" s="3" t="n">
-        <v>190</v>
-      </c>
-      <c r="K9" s="3" t="n">
-        <v>190</v>
-      </c>
-      <c r="L9" s="3" t="n">
-        <v>345</v>
-      </c>
-      <c r="M9" s="3" t="n">
-        <v>345</v>
+        <v>80</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>中续器</t>
+          <t>传送门</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -2748,38 +5786,15 @@
       <c r="D10" s="3" t="n">
         <v>35</v>
       </c>
-      <c r="E10" s="3" t="n">
-        <v>35</v>
-      </c>
-      <c r="F10" s="3" t="n">
-        <v>60</v>
-      </c>
-      <c r="G10" s="3" t="n">
-        <v>60</v>
-      </c>
-      <c r="H10" s="3" t="n">
-        <v>105</v>
-      </c>
-      <c r="I10" s="3" t="n">
-        <v>105</v>
-      </c>
-      <c r="J10" s="3" t="n">
-        <v>190</v>
-      </c>
-      <c r="K10" s="3" t="n">
-        <v>190</v>
-      </c>
-      <c r="L10" s="3" t="n">
-        <v>345</v>
-      </c>
-      <c r="M10" s="3" t="n">
-        <v>345</v>
-      </c>
+      <c r="E10" s="3" t="inlineStr"/>
+      <c r="F10" s="3" t="inlineStr"/>
+      <c r="G10" s="3" t="inlineStr"/>
+      <c r="H10" s="3" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>加速器</t>
+          <t>中续器</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
@@ -2788,43 +5803,20 @@
         </is>
       </c>
       <c r="C11" s="3" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D11" s="3" t="n">
-        <v>30</v>
-      </c>
-      <c r="E11" s="3" t="n">
-        <v>30</v>
-      </c>
-      <c r="F11" s="3" t="n">
-        <v>55</v>
-      </c>
-      <c r="G11" s="3" t="n">
-        <v>55</v>
-      </c>
-      <c r="H11" s="3" t="n">
-        <v>95</v>
-      </c>
-      <c r="I11" s="3" t="n">
-        <v>95</v>
-      </c>
-      <c r="J11" s="3" t="n">
-        <v>175</v>
-      </c>
-      <c r="K11" s="3" t="n">
-        <v>175</v>
-      </c>
-      <c r="L11" s="3" t="n">
-        <v>315</v>
-      </c>
-      <c r="M11" s="3" t="n">
-        <v>315</v>
-      </c>
+        <v>35</v>
+      </c>
+      <c r="E11" s="3" t="inlineStr"/>
+      <c r="F11" s="3" t="inlineStr"/>
+      <c r="G11" s="3" t="inlineStr"/>
+      <c r="H11" s="3" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>火附魔</t>
+          <t>加速器</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
@@ -2838,38 +5830,15 @@
       <c r="D12" s="3" t="n">
         <v>30</v>
       </c>
-      <c r="E12" s="3" t="n">
-        <v>30</v>
-      </c>
-      <c r="F12" s="3" t="n">
-        <v>55</v>
-      </c>
-      <c r="G12" s="3" t="n">
-        <v>55</v>
-      </c>
-      <c r="H12" s="3" t="n">
-        <v>95</v>
-      </c>
-      <c r="I12" s="3" t="n">
-        <v>95</v>
-      </c>
-      <c r="J12" s="3" t="n">
-        <v>175</v>
-      </c>
-      <c r="K12" s="3" t="n">
-        <v>175</v>
-      </c>
-      <c r="L12" s="3" t="n">
-        <v>315</v>
-      </c>
-      <c r="M12" s="3" t="n">
-        <v>315</v>
-      </c>
+      <c r="E12" s="3" t="inlineStr"/>
+      <c r="F12" s="3" t="inlineStr"/>
+      <c r="G12" s="3" t="inlineStr"/>
+      <c r="H12" s="3" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>惊喜</t>
+          <t>火附魔</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
@@ -2884,37 +5853,20 @@
         <v>30</v>
       </c>
       <c r="E13" s="3" t="n">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="F13" s="3" t="n">
         <v>55</v>
       </c>
       <c r="G13" s="3" t="n">
-        <v>55</v>
-      </c>
-      <c r="H13" s="3" t="n">
-        <v>95</v>
-      </c>
-      <c r="I13" s="3" t="n">
-        <v>95</v>
-      </c>
-      <c r="J13" s="3" t="n">
-        <v>175</v>
-      </c>
-      <c r="K13" s="3" t="n">
-        <v>175</v>
-      </c>
-      <c r="L13" s="3" t="n">
-        <v>315</v>
-      </c>
-      <c r="M13" s="3" t="n">
-        <v>315</v>
-      </c>
+        <v>65</v>
+      </c>
+      <c r="H13" s="3" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>热浪</t>
+          <t>惊喜</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -2923,218 +5875,333 @@
         </is>
       </c>
       <c r="C14" s="3" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="D14" s="3" t="n">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="E14" s="3" t="n">
         <v>40</v>
       </c>
       <c r="F14" s="3" t="n">
-        <v>70</v>
+        <v>55</v>
       </c>
       <c r="G14" s="3" t="n">
-        <v>70</v>
-      </c>
-      <c r="H14" s="3" t="n">
-        <v>120</v>
-      </c>
-      <c r="I14" s="3" t="n">
-        <v>120</v>
-      </c>
-      <c r="J14" s="3" t="n">
-        <v>220</v>
-      </c>
-      <c r="K14" s="3" t="n">
-        <v>220</v>
-      </c>
-      <c r="L14" s="3" t="n">
-        <v>395</v>
-      </c>
-      <c r="M14" s="3" t="n">
-        <v>395</v>
-      </c>
+        <v>65</v>
+      </c>
+      <c r="H14" s="3" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>黑洞</t>
+          <t>热浪</t>
         </is>
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>史诗</t>
+          <t>稀有</t>
         </is>
       </c>
       <c r="C15" s="3" t="n">
-        <v>45</v>
+        <v>25</v>
       </c>
       <c r="D15" s="3" t="n">
-        <v>110</v>
+        <v>40</v>
       </c>
       <c r="E15" s="3" t="n">
-        <v>110</v>
+        <v>90</v>
       </c>
       <c r="F15" s="3" t="n">
-        <v>200</v>
+        <v>205</v>
       </c>
       <c r="G15" s="3" t="n">
-        <v>200</v>
+        <v>485</v>
       </c>
       <c r="H15" s="3" t="n">
-        <v>365</v>
-      </c>
-      <c r="I15" s="3" t="n">
-        <v>365</v>
-      </c>
-      <c r="J15" s="3" t="n">
-        <v>655</v>
-      </c>
-      <c r="K15" s="3" t="n">
-        <v>655</v>
-      </c>
-      <c r="L15" s="3" t="n">
-        <v>1180</v>
-      </c>
-      <c r="M15" s="3" t="n">
-        <v>1180</v>
+        <v>1145</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
         <is>
-          <t>聚变</t>
+          <t>冰霜冻结</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>史诗</t>
+          <t>稀有</t>
         </is>
       </c>
       <c r="C16" s="3" t="n">
+        <v>25</v>
+      </c>
+      <c r="D16" s="3" t="n">
         <v>40</v>
       </c>
-      <c r="D16" s="3" t="n">
-        <v>100</v>
-      </c>
       <c r="E16" s="3" t="n">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>180</v>
+        <v>205</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>180</v>
+        <v>485</v>
       </c>
       <c r="H16" s="3" t="n">
-        <v>325</v>
-      </c>
-      <c r="I16" s="3" t="n">
-        <v>325</v>
-      </c>
-      <c r="J16" s="3" t="n">
-        <v>585</v>
-      </c>
-      <c r="K16" s="3" t="n">
-        <v>585</v>
-      </c>
-      <c r="L16" s="3" t="n">
-        <v>1050</v>
-      </c>
-      <c r="M16" s="3" t="n">
-        <v>1050</v>
+        <v>1145</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>裂变</t>
+          <t>奥数飞弹</t>
         </is>
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>史诗</t>
+          <t>稀有</t>
         </is>
       </c>
       <c r="C17" s="3" t="n">
-        <v>40</v>
+        <v>22</v>
       </c>
       <c r="D17" s="3" t="n">
-        <v>100</v>
+        <v>35</v>
       </c>
       <c r="E17" s="3" t="n">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="F17" s="3" t="n">
         <v>180</v>
       </c>
       <c r="G17" s="3" t="n">
-        <v>180</v>
+        <v>430</v>
       </c>
       <c r="H17" s="3" t="n">
-        <v>325</v>
-      </c>
-      <c r="I17" s="3" t="n">
-        <v>325</v>
-      </c>
-      <c r="J17" s="3" t="n">
-        <v>585</v>
-      </c>
-      <c r="K17" s="3" t="n">
-        <v>585</v>
-      </c>
-      <c r="L17" s="3" t="n">
-        <v>1050</v>
-      </c>
-      <c r="M17" s="3" t="n">
-        <v>1050</v>
+        <v>1005</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="3" t="inlineStr">
         <is>
+          <t>激光炮</t>
+        </is>
+      </c>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>普通</t>
+        </is>
+      </c>
+      <c r="C18" s="3" t="n">
+        <v>30</v>
+      </c>
+      <c r="D18" s="3" t="n">
+        <v>30</v>
+      </c>
+      <c r="E18" s="3" t="n">
+        <v>70</v>
+      </c>
+      <c r="F18" s="3" t="n">
+        <v>150</v>
+      </c>
+      <c r="G18" s="3" t="n">
+        <v>340</v>
+      </c>
+      <c r="H18" s="3" t="n">
+        <v>770</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="3" t="inlineStr">
+        <is>
+          <t>烈焰墙</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>稀有</t>
+        </is>
+      </c>
+      <c r="C19" s="3" t="n">
+        <v>28</v>
+      </c>
+      <c r="D19" s="3" t="n">
+        <v>40</v>
+      </c>
+      <c r="E19" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="F19" s="3" t="n">
+        <v>230</v>
+      </c>
+      <c r="G19" s="3" t="n">
+        <v>545</v>
+      </c>
+      <c r="H19" s="3" t="n">
+        <v>1280</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="3" t="inlineStr">
+        <is>
+          <t>火焰祝福</t>
+        </is>
+      </c>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>稀有</t>
+        </is>
+      </c>
+      <c r="C20" s="3" t="n">
+        <v>24</v>
+      </c>
+      <c r="D20" s="3" t="n">
+        <v>35</v>
+      </c>
+      <c r="E20" s="3" t="inlineStr"/>
+      <c r="F20" s="3" t="inlineStr"/>
+      <c r="G20" s="3" t="inlineStr"/>
+      <c r="H20" s="3" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="3" t="inlineStr">
+        <is>
+          <t>净化</t>
+        </is>
+      </c>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>稀有</t>
+        </is>
+      </c>
+      <c r="C21" s="3" t="n">
+        <v>28</v>
+      </c>
+      <c r="D21" s="3" t="n">
+        <v>40</v>
+      </c>
+      <c r="E21" s="3" t="inlineStr"/>
+      <c r="F21" s="3" t="inlineStr"/>
+      <c r="G21" s="3" t="inlineStr"/>
+      <c r="H21" s="3" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="3" t="inlineStr">
+        <is>
+          <t>寒霜蘑菇</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>稀有</t>
+        </is>
+      </c>
+      <c r="C22" s="3" t="n">
+        <v>28</v>
+      </c>
+      <c r="D22" s="3" t="n">
+        <v>40</v>
+      </c>
+      <c r="E22" s="3" t="inlineStr"/>
+      <c r="F22" s="3" t="inlineStr"/>
+      <c r="G22" s="3" t="inlineStr"/>
+      <c r="H22" s="3" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="3" t="inlineStr">
+        <is>
+          <t>黑洞</t>
+        </is>
+      </c>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>史诗</t>
+        </is>
+      </c>
+      <c r="C23" s="3" t="n">
+        <v>45</v>
+      </c>
+      <c r="D23" s="3" t="n">
+        <v>110</v>
+      </c>
+      <c r="E23" s="3" t="n">
+        <v>290</v>
+      </c>
+      <c r="F23" s="3" t="n">
+        <v>760</v>
+      </c>
+      <c r="G23" s="3" t="n">
+        <v>1975</v>
+      </c>
+      <c r="H23" s="3" t="n">
+        <v>5140</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="3" t="inlineStr">
+        <is>
+          <t>聚变</t>
+        </is>
+      </c>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>史诗</t>
+        </is>
+      </c>
+      <c r="C24" s="3" t="n">
+        <v>40</v>
+      </c>
+      <c r="D24" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="E24" s="3" t="inlineStr"/>
+      <c r="F24" s="3" t="inlineStr"/>
+      <c r="G24" s="3" t="inlineStr"/>
+      <c r="H24" s="3" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="3" t="inlineStr">
+        <is>
+          <t>裂变</t>
+        </is>
+      </c>
+      <c r="B25" s="3" t="inlineStr">
+        <is>
+          <t>史诗</t>
+        </is>
+      </c>
+      <c r="C25" s="3" t="n">
+        <v>40</v>
+      </c>
+      <c r="D25" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="E25" s="3" t="inlineStr"/>
+      <c r="F25" s="3" t="inlineStr"/>
+      <c r="G25" s="3" t="inlineStr"/>
+      <c r="H25" s="3" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="3" t="inlineStr">
+        <is>
           <t>分裂器</t>
         </is>
       </c>
-      <c r="B18" s="3" t="inlineStr">
+      <c r="B26" s="3" t="inlineStr">
         <is>
           <t>史诗</t>
         </is>
       </c>
-      <c r="C18" s="3" t="n">
+      <c r="C26" s="3" t="n">
         <v>55</v>
       </c>
-      <c r="D18" s="3" t="n">
+      <c r="D26" s="3" t="n">
         <v>140</v>
       </c>
-      <c r="E18" s="3" t="n">
-        <v>140</v>
-      </c>
-      <c r="F18" s="3" t="n">
-        <v>250</v>
-      </c>
-      <c r="G18" s="3" t="n">
-        <v>250</v>
-      </c>
-      <c r="H18" s="3" t="n">
-        <v>445</v>
-      </c>
-      <c r="I18" s="3" t="n">
-        <v>445</v>
-      </c>
-      <c r="J18" s="3" t="n">
-        <v>800</v>
-      </c>
-      <c r="K18" s="3" t="n">
-        <v>800</v>
-      </c>
-      <c r="L18" s="3" t="n">
-        <v>1445</v>
-      </c>
-      <c r="M18" s="3" t="n">
-        <v>1445</v>
-      </c>
+      <c r="E26" s="3" t="inlineStr"/>
+      <c r="F26" s="3" t="inlineStr"/>
+      <c r="G26" s="3" t="inlineStr"/>
+      <c r="H26" s="3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/docs/数值分析_模块怪物波次.xlsx
+++ b/docs/数值分析_模块怪物波次.xlsx
@@ -449,7 +449,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B16"/>
+  <dimension ref="A1:B17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -575,7 +575,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>26；波26仅 Boss HP=10000；Boss漏家即败</t>
+          <t>26；波26仅 Boss HP=50000；移速0.375；Boss漏家即败</t>
         </is>
       </c>
     </row>
@@ -606,10 +606,22 @@
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
+          <t>窗口化</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>1440×900；全屏=桌面分辨率</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
           <t>奥数飞弹</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
+      <c r="B17" t="inlineStr">
         <is>
           <t>稀有；能耗1/容5/射速5；伤10/20/30/50/80；最右索敌</t>
         </is>
@@ -626,7 +638,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C17"/>
+  <dimension ref="A1:C21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -684,7 +696,7 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>10000</v>
+        <v>50000</v>
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
@@ -695,205 +707,271 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>开局沙 ms</t>
+          <t>Boss 移速</t>
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>100000</v>
+        <v>0.375</v>
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>沙尽即败</t>
+          <t>坦克0.75的一半；单位格/秒</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>抽沙</t>
+          <t>红/黄/蓝移速</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>1000 ms/秒</t>
+          <t>1.5 / 3.0 / 0.75</t>
         </is>
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>仅战斗</t>
+          <t>紫拆·金盾同蓝</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>补沙</t>
-        </is>
-      </c>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>仅沙buff击杀</t>
-        </is>
+          <t>开局沙 ms</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="n">
+        <v>100000</v>
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>清波不补沙</t>
+          <t>沙尽即败</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>手牌/商店</t>
+          <t>抽沙</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>8 / 6</t>
-        </is>
-      </c>
-      <c r="C8" s="3" t="inlineStr"/>
+          <t>1000 ms/秒</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t>仅战斗</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>商店池上限</t>
-        </is>
-      </c>
-      <c r="B9" s="3" t="n">
-        <v>12</v>
+          <t>补沙</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>仅沙buff击杀</t>
+        </is>
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>开局：激光+收束+雪花+火花</t>
+          <t>清波不补沙</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>球上限</t>
-        </is>
-      </c>
-      <c r="B10" s="3" t="n">
-        <v>40</v>
+          <t>手牌/商店</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>8 / 6</t>
+        </is>
       </c>
       <c r="C10" s="3" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>球寿命档</t>
-        </is>
-      </c>
-      <c r="B11" s="3" t="inlineStr">
-        <is>
-          <t>12/20/32/50 s</t>
-        </is>
+          <t>商店池上限</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="n">
+        <v>12</v>
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>熔炉寿命维</t>
+          <t>开局：激光+收束+雪花+火花</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>分解返还</t>
+          <t>球上限</t>
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="C12" s="3" t="inlineStr">
-        <is>
-          <t>invested×30%</t>
-        </is>
-      </c>
+        <v>40</v>
+      </c>
+      <c r="C12" s="3" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>扩展费用</t>
+          <t>球寿命档</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>100 / 300</t>
+          <t>12/20/32/50 s</t>
         </is>
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>3→5 / 5→7</t>
+          <t>熔炉寿命维</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>刷新费</t>
+          <t>窗口化</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>5×((shopLv+1)/2)</t>
+          <t>1440×900</t>
         </is>
       </c>
       <c r="C14" s="3" t="inlineStr">
         <is>
-          <t>商店 Lv1–2→5，Lv3–4→10…</t>
+          <t>全屏=桌面分辨率</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>商店等级</t>
-        </is>
-      </c>
-      <c r="B15" s="3" t="inlineStr">
-        <is>
-          <t>(wave-1)//5+1</t>
-        </is>
+          <t>分解返还</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="n">
+        <v>0.3</v>
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>每5波升1级；奇级单档/偶级双档</t>
+          <t>invested×30%</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
         <is>
-          <t>模块解锁</t>
+          <t>扩展费用</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>前15每3波，后每2波</t>
+          <t>100 / 300</t>
         </is>
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
-          <t>3/6/9/12/16/18/20/22/24</t>
+          <t>3→5 / 5→7</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
+          <t>刷新费</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>5×((shopLv+1)/2)</t>
+        </is>
+      </c>
+      <c r="C17" s="3" t="inlineStr">
+        <is>
+          <t>商店 Lv1–2→5，Lv3–4→10…</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="3" t="inlineStr">
+        <is>
+          <t>商店等级</t>
+        </is>
+      </c>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>(wave-1)//5+1</t>
+        </is>
+      </c>
+      <c r="C18" s="3" t="inlineStr">
+        <is>
+          <t>每5波升1级；奇级单档/偶级双档</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="3" t="inlineStr">
+        <is>
+          <t>模块解锁</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>前15每3波，后每2波</t>
+        </is>
+      </c>
+      <c r="C19" s="3" t="inlineStr">
+        <is>
+          <t>3/6/9/12/16/18/20/22/24</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="3" t="inlineStr">
+        <is>
           <t>熔炉/祝福</t>
         </is>
       </c>
-      <c r="B17" s="3" t="inlineStr">
+      <c r="B20" s="3" t="inlineStr">
         <is>
           <t>每5波至25</t>
         </is>
       </c>
-      <c r="C17" s="3" t="inlineStr">
+      <c r="C20" s="3" t="inlineStr">
         <is>
           <t>5/10/15/20/25</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="3" t="inlineStr">
+        <is>
+          <t>胜负</t>
+        </is>
+      </c>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>返回主菜单</t>
+        </is>
+      </c>
+      <c r="C21" s="3" t="inlineStr">
+        <is>
+          <t>ResultOverlay</t>
         </is>
       </c>
     </row>
@@ -5461,14 +5539,14 @@
       <c r="G27" s="3" t="inlineStr"/>
       <c r="H27" s="3" t="inlineStr">
         <is>
-          <t>Boss 10000</t>
+          <t>Boss 50000</t>
         </is>
       </c>
       <c r="I27" s="3" t="n">
-        <v>10000</v>
+        <v>50000</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>-0.826</v>
+        <v>-0.132</v>
       </c>
       <c r="K27" s="3" t="n">
         <v>1905</v>
